--- a/data_generacion/serie_ingresos_generacion.xlsx
+++ b/data_generacion/serie_ingresos_generacion.xlsx
@@ -986,137 +986,137 @@
       </c>
       <c r="DH1" s="1" t="inlineStr">
         <is>
+          <t>Precio Monómico USD/MWh 032023</t>
+        </is>
+      </c>
+      <c r="DI1" s="1" t="inlineStr">
+        <is>
+          <t>Precio Monómico USD/MWh 102024</t>
+        </is>
+      </c>
+      <c r="DJ1" s="1" t="inlineStr">
+        <is>
+          <t>Precio Monómico USD/MWh 042023</t>
+        </is>
+      </c>
+      <c r="DK1" s="1" t="inlineStr">
+        <is>
+          <t>Precio Monómico USD/MWh 052024</t>
+        </is>
+      </c>
+      <c r="DL1" s="1" t="inlineStr">
+        <is>
+          <t>Precio Monómico USD/MWh 022024</t>
+        </is>
+      </c>
+      <c r="DM1" s="1" t="inlineStr">
+        <is>
+          <t>Precio Monómico USD/MWh 032024</t>
+        </is>
+      </c>
+      <c r="DN1" s="1" t="inlineStr">
+        <is>
+          <t>Precio Monómico USD/MWh 072023</t>
+        </is>
+      </c>
+      <c r="DO1" s="1" t="inlineStr">
+        <is>
+          <t>Precio Monómico USD/MWh 012024</t>
+        </is>
+      </c>
+      <c r="DP1" s="1" t="inlineStr">
+        <is>
+          <t>Precio Monómico USD/MWh 102023</t>
+        </is>
+      </c>
+      <c r="DQ1" s="1" t="inlineStr">
+        <is>
+          <t>Precio Monómico USD/MWh 122024</t>
+        </is>
+      </c>
+      <c r="DR1" s="1" t="inlineStr">
+        <is>
+          <t>Precio Monómico USD/MWh 122023</t>
+        </is>
+      </c>
+      <c r="DS1" s="1" t="inlineStr">
+        <is>
+          <t>Precio Monómico USD/MWh 022025</t>
+        </is>
+      </c>
+      <c r="DT1" s="1" t="inlineStr">
+        <is>
+          <t>Precio Monómico USD/MWh 072024</t>
+        </is>
+      </c>
+      <c r="DU1" s="1" t="inlineStr">
+        <is>
+          <t>Precio Monómico USD/MWh 082024</t>
+        </is>
+      </c>
+      <c r="DV1" s="1" t="inlineStr">
+        <is>
+          <t>Precio Monómico USD/MWh 022023</t>
+        </is>
+      </c>
+      <c r="DW1" s="1" t="inlineStr">
+        <is>
+          <t>Precio Monómico USD/MWh 112023</t>
+        </is>
+      </c>
+      <c r="DX1" s="1" t="inlineStr">
+        <is>
+          <t>Precio Monómico USD/MWh 112024</t>
+        </is>
+      </c>
+      <c r="DY1" s="1" t="inlineStr">
+        <is>
+          <t>Precio Monómico USD/MWh 092024</t>
+        </is>
+      </c>
+      <c r="DZ1" s="1" t="inlineStr">
+        <is>
           <t>Precio Monómico USD/MWh 012023</t>
         </is>
       </c>
-      <c r="DI1" s="1" t="inlineStr">
-        <is>
-          <t>Precio Monómico USD/MWh 022023</t>
-        </is>
-      </c>
-      <c r="DJ1" s="1" t="inlineStr">
-        <is>
-          <t>Precio Monómico USD/MWh 032023</t>
-        </is>
-      </c>
-      <c r="DK1" s="1" t="inlineStr">
-        <is>
-          <t>Precio Monómico USD/MWh 042023</t>
-        </is>
-      </c>
-      <c r="DL1" s="1" t="inlineStr">
+      <c r="EA1" s="1" t="inlineStr">
+        <is>
+          <t>Precio Monómico USD/MWh 062023</t>
+        </is>
+      </c>
+      <c r="EB1" s="1" t="inlineStr">
+        <is>
+          <t>Precio Monómico USD/MWh 012025</t>
+        </is>
+      </c>
+      <c r="EC1" s="1" t="inlineStr">
+        <is>
+          <t>Precio Monómico USD/MWh 062024</t>
+        </is>
+      </c>
+      <c r="ED1" s="1" t="inlineStr">
+        <is>
+          <t>Precio Monómico USD/MWh 072025</t>
+        </is>
+      </c>
+      <c r="EE1" s="1" t="inlineStr">
+        <is>
+          <t>Precio Monómico USD/MWh 092023</t>
+        </is>
+      </c>
+      <c r="EF1" s="1" t="inlineStr">
+        <is>
+          <t>Precio Monómico USD/MWh 042024</t>
+        </is>
+      </c>
+      <c r="EG1" s="1" t="inlineStr">
         <is>
           <t>Precio Monómico USD/MWh 052023</t>
         </is>
       </c>
-      <c r="DM1" s="1" t="inlineStr">
-        <is>
-          <t>Precio Monómico USD/MWh 062023</t>
-        </is>
-      </c>
-      <c r="DN1" s="1" t="inlineStr">
-        <is>
-          <t>Precio Monómico USD/MWh 072023</t>
-        </is>
-      </c>
-      <c r="DO1" s="1" t="inlineStr">
+      <c r="EH1" s="1" t="inlineStr">
         <is>
           <t>Precio Monómico USD/MWh 082023</t>
-        </is>
-      </c>
-      <c r="DP1" s="1" t="inlineStr">
-        <is>
-          <t>Precio Monómico USD/MWh 092023</t>
-        </is>
-      </c>
-      <c r="DQ1" s="1" t="inlineStr">
-        <is>
-          <t>Precio Monómico USD/MWh 102023</t>
-        </is>
-      </c>
-      <c r="DR1" s="1" t="inlineStr">
-        <is>
-          <t>Precio Monómico USD/MWh 112023</t>
-        </is>
-      </c>
-      <c r="DS1" s="1" t="inlineStr">
-        <is>
-          <t>Precio Monómico USD/MWh 122023</t>
-        </is>
-      </c>
-      <c r="DT1" s="1" t="inlineStr">
-        <is>
-          <t>Precio Monómico USD/MWh 012024</t>
-        </is>
-      </c>
-      <c r="DU1" s="1" t="inlineStr">
-        <is>
-          <t>Precio Monómico USD/MWh 022024</t>
-        </is>
-      </c>
-      <c r="DV1" s="1" t="inlineStr">
-        <is>
-          <t>Precio Monómico USD/MWh 032024</t>
-        </is>
-      </c>
-      <c r="DW1" s="1" t="inlineStr">
-        <is>
-          <t>Precio Monómico USD/MWh 042024</t>
-        </is>
-      </c>
-      <c r="DX1" s="1" t="inlineStr">
-        <is>
-          <t>Precio Monómico USD/MWh 052024</t>
-        </is>
-      </c>
-      <c r="DY1" s="1" t="inlineStr">
-        <is>
-          <t>Precio Monómico USD/MWh 062024</t>
-        </is>
-      </c>
-      <c r="DZ1" s="1" t="inlineStr">
-        <is>
-          <t>Precio Monómico USD/MWh 072024</t>
-        </is>
-      </c>
-      <c r="EA1" s="1" t="inlineStr">
-        <is>
-          <t>Precio Monómico USD/MWh 082024</t>
-        </is>
-      </c>
-      <c r="EB1" s="1" t="inlineStr">
-        <is>
-          <t>Precio Monómico USD/MWh 092024</t>
-        </is>
-      </c>
-      <c r="EC1" s="1" t="inlineStr">
-        <is>
-          <t>Precio Monómico USD/MWh 102024</t>
-        </is>
-      </c>
-      <c r="ED1" s="1" t="inlineStr">
-        <is>
-          <t>Precio Monómico USD/MWh 112024</t>
-        </is>
-      </c>
-      <c r="EE1" s="1" t="inlineStr">
-        <is>
-          <t>Precio Monómico USD/MWh 122024</t>
-        </is>
-      </c>
-      <c r="EF1" s="1" t="inlineStr">
-        <is>
-          <t>Precio Monómico USD/MWh 012025</t>
-        </is>
-      </c>
-      <c r="EG1" s="1" t="inlineStr">
-        <is>
-          <t>Precio Monómico USD/MWh 022025</t>
-        </is>
-      </c>
-      <c r="EH1" s="1" t="inlineStr">
-        <is>
-          <t>Precio Monómico USD/MWh 072025</t>
         </is>
       </c>
     </row>
@@ -1429,61 +1429,61 @@
         <v>32648.91</v>
       </c>
       <c r="DH2" t="inlineStr"/>
-      <c r="DI2" t="inlineStr"/>
+      <c r="DI2" t="n">
+        <v>32.58370444808919</v>
+      </c>
       <c r="DJ2" t="inlineStr"/>
-      <c r="DK2" t="inlineStr"/>
-      <c r="DL2" t="n">
-        <v>29.07392590251798</v>
-      </c>
-      <c r="DM2" t="n">
-        <v>29.36520340064861</v>
-      </c>
+      <c r="DK2" t="n">
+        <v>24.77923032651861</v>
+      </c>
+      <c r="DL2" t="inlineStr"/>
+      <c r="DM2" t="inlineStr"/>
       <c r="DN2" t="n">
         <v>33.84683953742918</v>
       </c>
-      <c r="DO2" t="n">
-        <v>68.84745583824021</v>
-      </c>
-      <c r="DP2" t="n">
-        <v>40.54372042235981</v>
-      </c>
+      <c r="DO2" t="inlineStr"/>
+      <c r="DP2" t="inlineStr"/>
       <c r="DQ2" t="inlineStr"/>
-      <c r="DR2" t="n">
-        <v>30.88729791128371</v>
-      </c>
+      <c r="DR2" t="inlineStr"/>
       <c r="DS2" t="inlineStr"/>
-      <c r="DT2" t="inlineStr"/>
-      <c r="DU2" t="inlineStr"/>
+      <c r="DT2" t="n">
+        <v>28.16774277831702</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>27.94464635618218</v>
+      </c>
       <c r="DV2" t="inlineStr"/>
       <c r="DW2" t="n">
+        <v>30.88729791128371</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>29.84369778359311</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>32.65773264124746</v>
+      </c>
+      <c r="DZ2" t="inlineStr"/>
+      <c r="EA2" t="n">
+        <v>29.36520340064861</v>
+      </c>
+      <c r="EB2" t="inlineStr"/>
+      <c r="EC2" t="n">
+        <v>27.45635271297863</v>
+      </c>
+      <c r="ED2" t="n">
+        <v>29.48317525099045</v>
+      </c>
+      <c r="EE2" t="n">
+        <v>40.54372042235981</v>
+      </c>
+      <c r="EF2" t="n">
         <v>16.50009501105583</v>
       </c>
-      <c r="DX2" t="n">
-        <v>24.77923032651861</v>
-      </c>
-      <c r="DY2" t="n">
-        <v>27.45635271297863</v>
-      </c>
-      <c r="DZ2" t="n">
-        <v>28.16774277831702</v>
-      </c>
-      <c r="EA2" t="n">
-        <v>27.94464635618218</v>
-      </c>
-      <c r="EB2" t="n">
-        <v>32.65773264124746</v>
-      </c>
-      <c r="EC2" t="n">
-        <v>32.58370444808919</v>
-      </c>
-      <c r="ED2" t="n">
-        <v>29.84369778359311</v>
-      </c>
-      <c r="EE2" t="inlineStr"/>
-      <c r="EF2" t="inlineStr"/>
-      <c r="EG2" t="inlineStr"/>
+      <c r="EG2" t="n">
+        <v>29.07392590251798</v>
+      </c>
       <c r="EH2" t="n">
-        <v>29.48317525099045</v>
+        <v>68.84745583824021</v>
       </c>
     </row>
     <row r="3">
@@ -1827,65 +1827,65 @@
         <v>447015.45</v>
       </c>
       <c r="DH3" t="inlineStr"/>
-      <c r="DI3" t="inlineStr"/>
-      <c r="DJ3" t="inlineStr"/>
+      <c r="DI3" t="n">
+        <v>32.29646004373615</v>
+      </c>
+      <c r="DJ3" t="n">
+        <v>28.55539627101774</v>
+      </c>
       <c r="DK3" t="n">
-        <v>28.55539627101774</v>
-      </c>
-      <c r="DL3" t="n">
-        <v>30.62074669060925</v>
-      </c>
-      <c r="DM3" t="n">
-        <v>29.83630411449049</v>
-      </c>
+        <v>28.52464577909023</v>
+      </c>
+      <c r="DL3" t="inlineStr"/>
+      <c r="DM3" t="inlineStr"/>
       <c r="DN3" t="n">
         <v>27.77668700157308</v>
       </c>
-      <c r="DO3" t="n">
-        <v>27.66436050492642</v>
-      </c>
+      <c r="DO3" t="inlineStr"/>
       <c r="DP3" t="n">
-        <v>28.35324969369688</v>
-      </c>
-      <c r="DQ3" t="n">
         <v>28.89561753362052</v>
       </c>
-      <c r="DR3" t="n">
-        <v>30.19895547241914</v>
-      </c>
+      <c r="DQ3" t="inlineStr"/>
+      <c r="DR3" t="inlineStr"/>
       <c r="DS3" t="inlineStr"/>
-      <c r="DT3" t="inlineStr"/>
-      <c r="DU3" t="inlineStr"/>
+      <c r="DT3" t="n">
+        <v>28.76970229807875</v>
+      </c>
+      <c r="DU3" t="n">
+        <v>29.05080781710329</v>
+      </c>
       <c r="DV3" t="inlineStr"/>
       <c r="DW3" t="n">
+        <v>30.19895547241914</v>
+      </c>
+      <c r="DX3" t="n">
+        <v>29.9822275262317</v>
+      </c>
+      <c r="DY3" t="n">
+        <v>33.17462776946449</v>
+      </c>
+      <c r="DZ3" t="inlineStr"/>
+      <c r="EA3" t="n">
+        <v>29.83630411449049</v>
+      </c>
+      <c r="EB3" t="inlineStr"/>
+      <c r="EC3" t="n">
+        <v>29.18284923343062</v>
+      </c>
+      <c r="ED3" t="n">
+        <v>28.85706877558908</v>
+      </c>
+      <c r="EE3" t="n">
+        <v>28.35324969369688</v>
+      </c>
+      <c r="EF3" t="n">
         <v>16.26874876652852</v>
       </c>
-      <c r="DX3" t="n">
-        <v>28.52464577909023</v>
-      </c>
-      <c r="DY3" t="n">
-        <v>29.18284923343062</v>
-      </c>
-      <c r="DZ3" t="n">
-        <v>28.76970229807875</v>
-      </c>
-      <c r="EA3" t="n">
-        <v>29.05080781710329</v>
-      </c>
-      <c r="EB3" t="n">
-        <v>33.17462776946449</v>
-      </c>
-      <c r="EC3" t="n">
-        <v>32.29646004373615</v>
-      </c>
-      <c r="ED3" t="n">
-        <v>29.9822275262317</v>
-      </c>
-      <c r="EE3" t="inlineStr"/>
-      <c r="EF3" t="inlineStr"/>
-      <c r="EG3" t="inlineStr"/>
+      <c r="EG3" t="n">
+        <v>30.62074669060925</v>
+      </c>
       <c r="EH3" t="n">
-        <v>28.85706877558908</v>
+        <v>27.66436050492642</v>
       </c>
     </row>
     <row r="4">
@@ -2229,85 +2229,85 @@
         <v>131302.8475</v>
       </c>
       <c r="DH4" t="n">
-        <v>35.37149982484486</v>
+        <v>35.31174682786317</v>
       </c>
       <c r="DI4" t="n">
-        <v>37.4329711413952</v>
+        <v>38.36691397485751</v>
       </c>
       <c r="DJ4" t="n">
-        <v>35.31174682786317</v>
+        <v>36.30403261914186</v>
       </c>
       <c r="DK4" t="n">
-        <v>36.30403261914186</v>
+        <v>39.9915578975083</v>
       </c>
       <c r="DL4" t="n">
-        <v>35.77263727708263</v>
+        <v>37.51903790158474</v>
       </c>
       <c r="DM4" t="n">
-        <v>38.95266531512424</v>
+        <v>36.33396690098421</v>
       </c>
       <c r="DN4" t="n">
         <v>36.53920303782283</v>
       </c>
       <c r="DO4" t="n">
+        <v>36.30603272728703</v>
+      </c>
+      <c r="DP4" t="n">
+        <v>36.54993931201319</v>
+      </c>
+      <c r="DQ4" t="n">
+        <v>90.35330743454539</v>
+      </c>
+      <c r="DR4" t="n">
+        <v>36.76323219102814</v>
+      </c>
+      <c r="DS4" t="n">
+        <v>109.8307570065166</v>
+      </c>
+      <c r="DT4" t="n">
+        <v>39.77758335861597</v>
+      </c>
+      <c r="DU4" t="n">
+        <v>39.43144019612724</v>
+      </c>
+      <c r="DV4" t="n">
+        <v>37.4329711413952</v>
+      </c>
+      <c r="DW4" t="n">
+        <v>36.43186311556198</v>
+      </c>
+      <c r="DX4" t="n">
+        <v>42.58932505517807</v>
+      </c>
+      <c r="DY4" t="n">
+        <v>38.94309583331059</v>
+      </c>
+      <c r="DZ4" t="n">
+        <v>35.37149982484486</v>
+      </c>
+      <c r="EA4" t="n">
+        <v>38.95266531512424</v>
+      </c>
+      <c r="EB4" t="n">
+        <v>120.0730229727502</v>
+      </c>
+      <c r="EC4" t="n">
+        <v>40.74328138342123</v>
+      </c>
+      <c r="ED4" t="n">
+        <v>125.3404836002865</v>
+      </c>
+      <c r="EE4" t="n">
+        <v>37.31199215702235</v>
+      </c>
+      <c r="EF4" t="n">
+        <v>37.39380718190807</v>
+      </c>
+      <c r="EG4" t="n">
+        <v>35.77263727708263</v>
+      </c>
+      <c r="EH4" t="n">
         <v>35.83813411588277</v>
-      </c>
-      <c r="DP4" t="n">
-        <v>37.31199215702235</v>
-      </c>
-      <c r="DQ4" t="n">
-        <v>36.54993931201319</v>
-      </c>
-      <c r="DR4" t="n">
-        <v>36.43186311556198</v>
-      </c>
-      <c r="DS4" t="n">
-        <v>36.76323219102814</v>
-      </c>
-      <c r="DT4" t="n">
-        <v>36.30603272728703</v>
-      </c>
-      <c r="DU4" t="n">
-        <v>37.51903790158474</v>
-      </c>
-      <c r="DV4" t="n">
-        <v>36.33396690098421</v>
-      </c>
-      <c r="DW4" t="n">
-        <v>37.39380718190807</v>
-      </c>
-      <c r="DX4" t="n">
-        <v>39.9915578975083</v>
-      </c>
-      <c r="DY4" t="n">
-        <v>40.74328138342123</v>
-      </c>
-      <c r="DZ4" t="n">
-        <v>39.77758335861597</v>
-      </c>
-      <c r="EA4" t="n">
-        <v>39.43144019612724</v>
-      </c>
-      <c r="EB4" t="n">
-        <v>38.94309583331059</v>
-      </c>
-      <c r="EC4" t="n">
-        <v>38.36691397485751</v>
-      </c>
-      <c r="ED4" t="n">
-        <v>42.58932505517807</v>
-      </c>
-      <c r="EE4" t="n">
-        <v>90.35330743454539</v>
-      </c>
-      <c r="EF4" t="n">
-        <v>120.0730229727502</v>
-      </c>
-      <c r="EG4" t="n">
-        <v>109.8307570065166</v>
-      </c>
-      <c r="EH4" t="n">
-        <v>125.3404836002865</v>
       </c>
     </row>
     <row r="5">
@@ -2651,74 +2651,74 @@
         <v>0</v>
       </c>
       <c r="DH5" t="n">
-        <v>15.4001273044877</v>
+        <v>15.34844061260092</v>
       </c>
       <c r="DI5" t="n">
-        <v>15.31929957898372</v>
+        <v>20.77313536162011</v>
       </c>
       <c r="DJ5" t="n">
-        <v>15.34844061260092</v>
+        <v>16.32703653241697</v>
       </c>
       <c r="DK5" t="n">
-        <v>16.32703653241697</v>
+        <v>60.22149188541086</v>
       </c>
       <c r="DL5" t="n">
-        <v>15.62656315529412</v>
-      </c>
-      <c r="DM5" t="n">
-        <v>15.64064387762306</v>
-      </c>
+        <v>41.2812017224774</v>
+      </c>
+      <c r="DM5" t="inlineStr"/>
       <c r="DN5" t="n">
         <v>24.54205764498463</v>
       </c>
       <c r="DO5" t="n">
+        <v>31.17457420329037</v>
+      </c>
+      <c r="DP5" t="n">
+        <v>29.04906127265116</v>
+      </c>
+      <c r="DQ5" t="inlineStr"/>
+      <c r="DR5" t="n">
+        <v>36.07061632098761</v>
+      </c>
+      <c r="DS5" t="inlineStr"/>
+      <c r="DT5" t="n">
+        <v>15.52937472634193</v>
+      </c>
+      <c r="DU5" t="n">
+        <v>15.64814259381078</v>
+      </c>
+      <c r="DV5" t="n">
+        <v>15.31929957898372</v>
+      </c>
+      <c r="DW5" t="n">
+        <v>26.19614009949898</v>
+      </c>
+      <c r="DX5" t="n">
+        <v>31.06620049565989</v>
+      </c>
+      <c r="DY5" t="n">
+        <v>16.10186166648608</v>
+      </c>
+      <c r="DZ5" t="n">
+        <v>15.4001273044877</v>
+      </c>
+      <c r="EA5" t="n">
+        <v>15.64064387762306</v>
+      </c>
+      <c r="EB5" t="inlineStr"/>
+      <c r="EC5" t="n">
+        <v>20.47271532784285</v>
+      </c>
+      <c r="ED5" t="inlineStr"/>
+      <c r="EE5" t="n">
+        <v>28.52467980551159</v>
+      </c>
+      <c r="EF5" t="inlineStr"/>
+      <c r="EG5" t="n">
+        <v>15.62656315529412</v>
+      </c>
+      <c r="EH5" t="n">
         <v>22.28525209069402</v>
       </c>
-      <c r="DP5" t="n">
-        <v>28.52467980551159</v>
-      </c>
-      <c r="DQ5" t="n">
-        <v>29.04906127265116</v>
-      </c>
-      <c r="DR5" t="n">
-        <v>26.19614009949898</v>
-      </c>
-      <c r="DS5" t="n">
-        <v>36.07061632098761</v>
-      </c>
-      <c r="DT5" t="n">
-        <v>31.17457420329037</v>
-      </c>
-      <c r="DU5" t="n">
-        <v>41.2812017224774</v>
-      </c>
-      <c r="DV5" t="inlineStr"/>
-      <c r="DW5" t="inlineStr"/>
-      <c r="DX5" t="n">
-        <v>60.22149188541086</v>
-      </c>
-      <c r="DY5" t="n">
-        <v>20.47271532784285</v>
-      </c>
-      <c r="DZ5" t="n">
-        <v>15.52937472634193</v>
-      </c>
-      <c r="EA5" t="n">
-        <v>15.64814259381078</v>
-      </c>
-      <c r="EB5" t="n">
-        <v>16.10186166648608</v>
-      </c>
-      <c r="EC5" t="n">
-        <v>20.77313536162011</v>
-      </c>
-      <c r="ED5" t="n">
-        <v>31.06620049565989</v>
-      </c>
-      <c r="EE5" t="inlineStr"/>
-      <c r="EF5" t="inlineStr"/>
-      <c r="EG5" t="inlineStr"/>
-      <c r="EH5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3429,84 +3429,84 @@
         <v>363594.315</v>
       </c>
       <c r="DH7" t="n">
-        <v>83.19074943350385</v>
+        <v>42.78550747333337</v>
       </c>
       <c r="DI7" t="n">
-        <v>627.8687118649749</v>
+        <v>29.5082103294153</v>
       </c>
       <c r="DJ7" t="n">
-        <v>42.78550747333337</v>
+        <v>48.1462514914342</v>
       </c>
       <c r="DK7" t="n">
-        <v>48.1462514914342</v>
+        <v>35.21579258410437</v>
       </c>
       <c r="DL7" t="n">
-        <v>26.50824932273393</v>
+        <v>20.51869691264709</v>
       </c>
       <c r="DM7" t="n">
-        <v>20.54446529168695</v>
+        <v>95.69380585508098</v>
       </c>
       <c r="DN7" t="n">
         <v>664.394661626406</v>
       </c>
       <c r="DO7" t="n">
+        <v>20.28612165697432</v>
+      </c>
+      <c r="DP7" t="n">
+        <v>77.53732284772941</v>
+      </c>
+      <c r="DQ7" t="n">
+        <v>145.8133932493659</v>
+      </c>
+      <c r="DR7" t="n">
+        <v>22.28092620197615</v>
+      </c>
+      <c r="DS7" t="n">
+        <v>134.1310477224227</v>
+      </c>
+      <c r="DT7" t="n">
+        <v>43.73954996062914</v>
+      </c>
+      <c r="DU7" t="n">
+        <v>57.80699425796161</v>
+      </c>
+      <c r="DV7" t="n">
+        <v>627.8687118649749</v>
+      </c>
+      <c r="DW7" t="n">
+        <v>20.21504570520197</v>
+      </c>
+      <c r="DX7" t="n">
+        <v>169.3399574095814</v>
+      </c>
+      <c r="DY7" t="n">
+        <v>23.45821629814511</v>
+      </c>
+      <c r="DZ7" t="n">
+        <v>83.19074943350385</v>
+      </c>
+      <c r="EA7" t="n">
+        <v>20.54446529168695</v>
+      </c>
+      <c r="EB7" t="n">
+        <v>229.3144326901414</v>
+      </c>
+      <c r="EC7" t="n">
+        <v>42.41320802287299</v>
+      </c>
+      <c r="ED7" t="inlineStr"/>
+      <c r="EE7" t="n">
+        <v>338.9634428124706</v>
+      </c>
+      <c r="EF7" t="n">
+        <v>306.658706980496</v>
+      </c>
+      <c r="EG7" t="n">
+        <v>26.50824932273393</v>
+      </c>
+      <c r="EH7" t="n">
         <v>198.4121785124679</v>
       </c>
-      <c r="DP7" t="n">
-        <v>338.9634428124706</v>
-      </c>
-      <c r="DQ7" t="n">
-        <v>77.53732284772941</v>
-      </c>
-      <c r="DR7" t="n">
-        <v>20.21504570520197</v>
-      </c>
-      <c r="DS7" t="n">
-        <v>22.28092620197615</v>
-      </c>
-      <c r="DT7" t="n">
-        <v>20.28612165697432</v>
-      </c>
-      <c r="DU7" t="n">
-        <v>20.51869691264709</v>
-      </c>
-      <c r="DV7" t="n">
-        <v>95.69380585508098</v>
-      </c>
-      <c r="DW7" t="n">
-        <v>306.658706980496</v>
-      </c>
-      <c r="DX7" t="n">
-        <v>35.21579258410437</v>
-      </c>
-      <c r="DY7" t="n">
-        <v>42.41320802287299</v>
-      </c>
-      <c r="DZ7" t="n">
-        <v>43.73954996062914</v>
-      </c>
-      <c r="EA7" t="n">
-        <v>57.80699425796161</v>
-      </c>
-      <c r="EB7" t="n">
-        <v>23.45821629814511</v>
-      </c>
-      <c r="EC7" t="n">
-        <v>29.5082103294153</v>
-      </c>
-      <c r="ED7" t="n">
-        <v>169.3399574095814</v>
-      </c>
-      <c r="EE7" t="n">
-        <v>145.8133932493659</v>
-      </c>
-      <c r="EF7" t="n">
-        <v>229.3144326901414</v>
-      </c>
-      <c r="EG7" t="n">
-        <v>134.1310477224227</v>
-      </c>
-      <c r="EH7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4217,85 +4217,85 @@
         <v>608640.4870000001</v>
       </c>
       <c r="DH9" t="n">
-        <v>92.37067779181366</v>
+        <v>1065.85613142264</v>
       </c>
       <c r="DI9" t="n">
-        <v>1347.708163270321</v>
+        <v>42.24272231453564</v>
       </c>
       <c r="DJ9" t="n">
-        <v>1065.85613142264</v>
+        <v>153.3528324165581</v>
       </c>
       <c r="DK9" t="n">
-        <v>153.3528324165581</v>
+        <v>33.88642424231299</v>
       </c>
       <c r="DL9" t="n">
-        <v>120.3443877513343</v>
+        <v>58.63132642248583</v>
       </c>
       <c r="DM9" t="n">
-        <v>60.2280479010661</v>
+        <v>29.83698300019259</v>
       </c>
       <c r="DN9" t="n">
         <v>52.78760089664635</v>
       </c>
       <c r="DO9" t="n">
+        <v>88.96900458437706</v>
+      </c>
+      <c r="DP9" t="n">
+        <v>46.78871074161842</v>
+      </c>
+      <c r="DQ9" t="n">
+        <v>43.72151142290484</v>
+      </c>
+      <c r="DR9" t="n">
+        <v>36.71287248760395</v>
+      </c>
+      <c r="DS9" t="n">
+        <v>56.00421576730673</v>
+      </c>
+      <c r="DT9" t="n">
+        <v>33.19838160747927</v>
+      </c>
+      <c r="DU9" t="n">
+        <v>38.74380409750004</v>
+      </c>
+      <c r="DV9" t="n">
+        <v>1347.708163270321</v>
+      </c>
+      <c r="DW9" t="n">
+        <v>46.08416546430153</v>
+      </c>
+      <c r="DX9" t="n">
+        <v>47.4398407794791</v>
+      </c>
+      <c r="DY9" t="n">
+        <v>39.82793345130408</v>
+      </c>
+      <c r="DZ9" t="n">
+        <v>92.37067779181366</v>
+      </c>
+      <c r="EA9" t="n">
+        <v>60.2280479010661</v>
+      </c>
+      <c r="EB9" t="n">
+        <v>44.6946533643796</v>
+      </c>
+      <c r="EC9" t="n">
+        <v>33.72656139443838</v>
+      </c>
+      <c r="ED9" t="n">
+        <v>30.98162419751872</v>
+      </c>
+      <c r="EE9" t="n">
+        <v>50.96534432804161</v>
+      </c>
+      <c r="EF9" t="n">
+        <v>31.13502224138588</v>
+      </c>
+      <c r="EG9" t="n">
+        <v>120.3443877513343</v>
+      </c>
+      <c r="EH9" t="n">
         <v>48.11876099801508</v>
-      </c>
-      <c r="DP9" t="n">
-        <v>50.96534432804161</v>
-      </c>
-      <c r="DQ9" t="n">
-        <v>46.78871074161842</v>
-      </c>
-      <c r="DR9" t="n">
-        <v>46.08416546430153</v>
-      </c>
-      <c r="DS9" t="n">
-        <v>36.71287248760395</v>
-      </c>
-      <c r="DT9" t="n">
-        <v>88.96900458437706</v>
-      </c>
-      <c r="DU9" t="n">
-        <v>58.63132642248583</v>
-      </c>
-      <c r="DV9" t="n">
-        <v>29.83698300019259</v>
-      </c>
-      <c r="DW9" t="n">
-        <v>31.13502224138588</v>
-      </c>
-      <c r="DX9" t="n">
-        <v>33.88642424231299</v>
-      </c>
-      <c r="DY9" t="n">
-        <v>33.72656139443838</v>
-      </c>
-      <c r="DZ9" t="n">
-        <v>33.19838160747927</v>
-      </c>
-      <c r="EA9" t="n">
-        <v>38.74380409750004</v>
-      </c>
-      <c r="EB9" t="n">
-        <v>39.82793345130408</v>
-      </c>
-      <c r="EC9" t="n">
-        <v>42.24272231453564</v>
-      </c>
-      <c r="ED9" t="n">
-        <v>47.4398407794791</v>
-      </c>
-      <c r="EE9" t="n">
-        <v>43.72151142290484</v>
-      </c>
-      <c r="EF9" t="n">
-        <v>44.6946533643796</v>
-      </c>
-      <c r="EG9" t="n">
-        <v>56.00421576730673</v>
-      </c>
-      <c r="EH9" t="n">
-        <v>30.98162419751872</v>
       </c>
     </row>
     <row r="10">
@@ -4639,85 +4639,85 @@
         <v>291174.888021616</v>
       </c>
       <c r="DH10" t="n">
-        <v>29.0439023271741</v>
+        <v>28.36629825348665</v>
       </c>
       <c r="DI10" t="n">
-        <v>26.89264651919627</v>
+        <v>94.28273379429433</v>
       </c>
       <c r="DJ10" t="n">
-        <v>28.36629825348665</v>
+        <v>30.66451478388082</v>
       </c>
       <c r="DK10" t="n">
-        <v>30.66451478388082</v>
+        <v>43.40581917649563</v>
       </c>
       <c r="DL10" t="n">
-        <v>35.39981995908001</v>
+        <v>38.79597464979638</v>
       </c>
       <c r="DM10" t="n">
-        <v>66.53440953580119</v>
+        <v>31.37459401211925</v>
       </c>
       <c r="DN10" t="n">
         <v>100.4248958216547</v>
       </c>
       <c r="DO10" t="n">
+        <v>44.63209138094926</v>
+      </c>
+      <c r="DP10" t="n">
+        <v>63.46864282675184</v>
+      </c>
+      <c r="DQ10" t="n">
+        <v>29.92097689303102</v>
+      </c>
+      <c r="DR10" t="n">
+        <v>27.5202800611277</v>
+      </c>
+      <c r="DS10" t="n">
+        <v>31.0360672401836</v>
+      </c>
+      <c r="DT10" t="n">
+        <v>69.66078102475798</v>
+      </c>
+      <c r="DU10" t="n">
+        <v>74.515155716951</v>
+      </c>
+      <c r="DV10" t="n">
+        <v>26.89264651919627</v>
+      </c>
+      <c r="DW10" t="n">
+        <v>41.83777696416923</v>
+      </c>
+      <c r="DX10" t="n">
+        <v>34.68104348607179</v>
+      </c>
+      <c r="DY10" t="n">
+        <v>136.7488433225722</v>
+      </c>
+      <c r="DZ10" t="n">
+        <v>29.0439023271741</v>
+      </c>
+      <c r="EA10" t="n">
+        <v>66.53440953580119</v>
+      </c>
+      <c r="EB10" t="n">
+        <v>29.23277392797157</v>
+      </c>
+      <c r="EC10" t="n">
+        <v>69.30028188036324</v>
+      </c>
+      <c r="ED10" t="n">
+        <v>71.75415411834751</v>
+      </c>
+      <c r="EE10" t="n">
+        <v>196.6051913881548</v>
+      </c>
+      <c r="EF10" t="n">
+        <v>34.37987735010693</v>
+      </c>
+      <c r="EG10" t="n">
+        <v>35.39981995908001</v>
+      </c>
+      <c r="EH10" t="n">
         <v>122.6921670950248</v>
-      </c>
-      <c r="DP10" t="n">
-        <v>196.6051913881548</v>
-      </c>
-      <c r="DQ10" t="n">
-        <v>63.46864282675184</v>
-      </c>
-      <c r="DR10" t="n">
-        <v>41.83777696416923</v>
-      </c>
-      <c r="DS10" t="n">
-        <v>27.5202800611277</v>
-      </c>
-      <c r="DT10" t="n">
-        <v>44.63209138094926</v>
-      </c>
-      <c r="DU10" t="n">
-        <v>38.79597464979638</v>
-      </c>
-      <c r="DV10" t="n">
-        <v>31.37459401211925</v>
-      </c>
-      <c r="DW10" t="n">
-        <v>34.37987735010693</v>
-      </c>
-      <c r="DX10" t="n">
-        <v>43.40581917649563</v>
-      </c>
-      <c r="DY10" t="n">
-        <v>69.30028188036324</v>
-      </c>
-      <c r="DZ10" t="n">
-        <v>69.66078102475798</v>
-      </c>
-      <c r="EA10" t="n">
-        <v>74.515155716951</v>
-      </c>
-      <c r="EB10" t="n">
-        <v>136.7488433225722</v>
-      </c>
-      <c r="EC10" t="n">
-        <v>94.28273379429433</v>
-      </c>
-      <c r="ED10" t="n">
-        <v>34.68104348607179</v>
-      </c>
-      <c r="EE10" t="n">
-        <v>29.92097689303102</v>
-      </c>
-      <c r="EF10" t="n">
-        <v>29.23277392797157</v>
-      </c>
-      <c r="EG10" t="n">
-        <v>31.0360672401836</v>
-      </c>
-      <c r="EH10" t="n">
-        <v>71.75415411834751</v>
       </c>
     </row>
     <row r="11">
@@ -5061,85 +5061,85 @@
         <v>1591887.48425</v>
       </c>
       <c r="DH11" t="n">
-        <v>27.09994727986151</v>
+        <v>25.54088600026869</v>
       </c>
       <c r="DI11" t="n">
-        <v>28.21304601617853</v>
+        <v>28.8893160787571</v>
       </c>
       <c r="DJ11" t="n">
-        <v>25.54088600026869</v>
+        <v>29.08514465479041</v>
       </c>
       <c r="DK11" t="n">
-        <v>29.08514465479041</v>
+        <v>25.2673799706842</v>
       </c>
       <c r="DL11" t="n">
-        <v>31.46831993379477</v>
+        <v>28.05216105519841</v>
       </c>
       <c r="DM11" t="n">
-        <v>27.71360040803502</v>
+        <v>28.12453366813647</v>
       </c>
       <c r="DN11" t="n">
         <v>25.78798212836393</v>
       </c>
       <c r="DO11" t="n">
+        <v>27.49984902087451</v>
+      </c>
+      <c r="DP11" t="n">
+        <v>26.62808763142681</v>
+      </c>
+      <c r="DQ11" t="n">
+        <v>27.60070075758065</v>
+      </c>
+      <c r="DR11" t="n">
+        <v>25.9819215242894</v>
+      </c>
+      <c r="DS11" t="n">
+        <v>29.42484955781713</v>
+      </c>
+      <c r="DT11" t="n">
+        <v>25.93069211957757</v>
+      </c>
+      <c r="DU11" t="n">
+        <v>26.22994720156758</v>
+      </c>
+      <c r="DV11" t="n">
+        <v>28.21304601617853</v>
+      </c>
+      <c r="DW11" t="n">
+        <v>27.95016712724552</v>
+      </c>
+      <c r="DX11" t="n">
+        <v>27.3363125261887</v>
+      </c>
+      <c r="DY11" t="n">
+        <v>28.76944385715591</v>
+      </c>
+      <c r="DZ11" t="n">
+        <v>27.09994727986151</v>
+      </c>
+      <c r="EA11" t="n">
+        <v>27.71360040803502</v>
+      </c>
+      <c r="EB11" t="n">
+        <v>28.5443131740296</v>
+      </c>
+      <c r="EC11" t="n">
+        <v>26.42419571070032</v>
+      </c>
+      <c r="ED11" t="n">
+        <v>27.71699606307712</v>
+      </c>
+      <c r="EE11" t="n">
+        <v>26.44950004836579</v>
+      </c>
+      <c r="EF11" t="n">
+        <v>27.28809622903572</v>
+      </c>
+      <c r="EG11" t="n">
+        <v>31.46831993379477</v>
+      </c>
+      <c r="EH11" t="n">
         <v>26.59563555495749</v>
-      </c>
-      <c r="DP11" t="n">
-        <v>26.44950004836579</v>
-      </c>
-      <c r="DQ11" t="n">
-        <v>26.62808763142681</v>
-      </c>
-      <c r="DR11" t="n">
-        <v>27.95016712724552</v>
-      </c>
-      <c r="DS11" t="n">
-        <v>25.9819215242894</v>
-      </c>
-      <c r="DT11" t="n">
-        <v>27.49984902087451</v>
-      </c>
-      <c r="DU11" t="n">
-        <v>28.05216105519841</v>
-      </c>
-      <c r="DV11" t="n">
-        <v>28.12453366813647</v>
-      </c>
-      <c r="DW11" t="n">
-        <v>27.28809622903572</v>
-      </c>
-      <c r="DX11" t="n">
-        <v>25.2673799706842</v>
-      </c>
-      <c r="DY11" t="n">
-        <v>26.42419571070032</v>
-      </c>
-      <c r="DZ11" t="n">
-        <v>25.93069211957757</v>
-      </c>
-      <c r="EA11" t="n">
-        <v>26.22994720156758</v>
-      </c>
-      <c r="EB11" t="n">
-        <v>28.76944385715591</v>
-      </c>
-      <c r="EC11" t="n">
-        <v>28.8893160787571</v>
-      </c>
-      <c r="ED11" t="n">
-        <v>27.3363125261887</v>
-      </c>
-      <c r="EE11" t="n">
-        <v>27.60070075758065</v>
-      </c>
-      <c r="EF11" t="n">
-        <v>28.5443131740296</v>
-      </c>
-      <c r="EG11" t="n">
-        <v>29.42484955781713</v>
-      </c>
-      <c r="EH11" t="n">
-        <v>27.71699606307712</v>
       </c>
     </row>
     <row r="12">
@@ -5499,12 +5499,12 @@
       <c r="DV12" t="inlineStr"/>
       <c r="DW12" t="inlineStr"/>
       <c r="DX12" t="inlineStr"/>
-      <c r="DY12" t="inlineStr"/>
+      <c r="DY12" t="n">
+        <v>26.98690574903262</v>
+      </c>
       <c r="DZ12" t="inlineStr"/>
       <c r="EA12" t="inlineStr"/>
-      <c r="EB12" t="n">
-        <v>26.98690574903262</v>
-      </c>
+      <c r="EB12" t="inlineStr"/>
       <c r="EC12" t="inlineStr"/>
       <c r="ED12" t="inlineStr"/>
       <c r="EE12" t="inlineStr"/>
@@ -5853,85 +5853,85 @@
         <v>2584947.813</v>
       </c>
       <c r="DH13" t="n">
-        <v>22.98314385517608</v>
+        <v>21.49762769647854</v>
       </c>
       <c r="DI13" t="n">
-        <v>25.38573159686203</v>
+        <v>31.81654851429649</v>
       </c>
       <c r="DJ13" t="n">
-        <v>21.49762769647854</v>
+        <v>24.54671538352397</v>
       </c>
       <c r="DK13" t="n">
-        <v>24.54671538352397</v>
+        <v>32.04060650568547</v>
       </c>
       <c r="DL13" t="n">
-        <v>28.62552465498747</v>
+        <v>33.54487590799539</v>
       </c>
       <c r="DM13" t="n">
-        <v>29.84365499646447</v>
+        <v>33.28575680250727</v>
       </c>
       <c r="DN13" t="n">
         <v>24.9100622089184</v>
       </c>
       <c r="DO13" t="n">
+        <v>32.15238261962588</v>
+      </c>
+      <c r="DP13" t="n">
+        <v>19.0302849801956</v>
+      </c>
+      <c r="DQ13" t="n">
+        <v>31.3911285439742</v>
+      </c>
+      <c r="DR13" t="n">
+        <v>38.4080241988524</v>
+      </c>
+      <c r="DS13" t="n">
+        <v>31.38474472987971</v>
+      </c>
+      <c r="DT13" t="n">
+        <v>30.4299865440722</v>
+      </c>
+      <c r="DU13" t="n">
+        <v>28.80977202337206</v>
+      </c>
+      <c r="DV13" t="n">
+        <v>25.38573159686203</v>
+      </c>
+      <c r="DW13" t="n">
+        <v>31.6125032100306</v>
+      </c>
+      <c r="DX13" t="n">
+        <v>30.28061759298714</v>
+      </c>
+      <c r="DY13" t="n">
+        <v>31.92996585340164</v>
+      </c>
+      <c r="DZ13" t="n">
+        <v>22.98314385517608</v>
+      </c>
+      <c r="EA13" t="n">
+        <v>29.84365499646447</v>
+      </c>
+      <c r="EB13" t="n">
+        <v>31.50519461957604</v>
+      </c>
+      <c r="EC13" t="n">
+        <v>32.43797577026582</v>
+      </c>
+      <c r="ED13" t="n">
+        <v>33.0202846784115</v>
+      </c>
+      <c r="EE13" t="n">
+        <v>21.58775912129013</v>
+      </c>
+      <c r="EF13" t="n">
+        <v>32.87438925580522</v>
+      </c>
+      <c r="EG13" t="n">
+        <v>28.62552465498747</v>
+      </c>
+      <c r="EH13" t="n">
         <v>24.57150706051403</v>
-      </c>
-      <c r="DP13" t="n">
-        <v>21.58775912129013</v>
-      </c>
-      <c r="DQ13" t="n">
-        <v>19.0302849801956</v>
-      </c>
-      <c r="DR13" t="n">
-        <v>31.6125032100306</v>
-      </c>
-      <c r="DS13" t="n">
-        <v>38.4080241988524</v>
-      </c>
-      <c r="DT13" t="n">
-        <v>32.15238261962588</v>
-      </c>
-      <c r="DU13" t="n">
-        <v>33.54487590799539</v>
-      </c>
-      <c r="DV13" t="n">
-        <v>33.28575680250727</v>
-      </c>
-      <c r="DW13" t="n">
-        <v>32.87438925580522</v>
-      </c>
-      <c r="DX13" t="n">
-        <v>32.04060650568547</v>
-      </c>
-      <c r="DY13" t="n">
-        <v>32.43797577026582</v>
-      </c>
-      <c r="DZ13" t="n">
-        <v>30.4299865440722</v>
-      </c>
-      <c r="EA13" t="n">
-        <v>28.80977202337206</v>
-      </c>
-      <c r="EB13" t="n">
-        <v>31.92996585340164</v>
-      </c>
-      <c r="EC13" t="n">
-        <v>31.81654851429649</v>
-      </c>
-      <c r="ED13" t="n">
-        <v>30.28061759298714</v>
-      </c>
-      <c r="EE13" t="n">
-        <v>31.3911285439742</v>
-      </c>
-      <c r="EF13" t="n">
-        <v>31.50519461957604</v>
-      </c>
-      <c r="EG13" t="n">
-        <v>31.38474472987971</v>
-      </c>
-      <c r="EH13" t="n">
-        <v>33.0202846784115</v>
       </c>
     </row>
     <row r="14">
@@ -6275,85 +6275,85 @@
         <v>0</v>
       </c>
       <c r="DH14" t="n">
-        <v>56.00360982410702</v>
+        <v>58.46016475451889</v>
       </c>
       <c r="DI14" t="n">
-        <v>55.03321293781833</v>
+        <v>76.06188777917092</v>
       </c>
       <c r="DJ14" t="n">
-        <v>58.46016475451889</v>
+        <v>57.42450387614548</v>
       </c>
       <c r="DK14" t="n">
-        <v>57.42450387614548</v>
+        <v>57.36781868516248</v>
       </c>
       <c r="DL14" t="n">
-        <v>61.71910044551651</v>
+        <v>59.99268223964041</v>
       </c>
       <c r="DM14" t="n">
-        <v>59.00950150134857</v>
+        <v>59.75778773943138</v>
       </c>
       <c r="DN14" t="n">
         <v>55.82656408923269</v>
       </c>
       <c r="DO14" t="n">
+        <v>59.66634940560481</v>
+      </c>
+      <c r="DP14" t="n">
+        <v>61.8487602337673</v>
+      </c>
+      <c r="DQ14" t="n">
+        <v>62.88482941911205</v>
+      </c>
+      <c r="DR14" t="n">
+        <v>57.17305092357412</v>
+      </c>
+      <c r="DS14" t="n">
+        <v>67.79353601209482</v>
+      </c>
+      <c r="DT14" t="n">
+        <v>57.44158402253986</v>
+      </c>
+      <c r="DU14" t="n">
+        <v>58.79575680475884</v>
+      </c>
+      <c r="DV14" t="n">
+        <v>55.03321293781833</v>
+      </c>
+      <c r="DW14" t="n">
+        <v>63.52494797753565</v>
+      </c>
+      <c r="DX14" t="n">
+        <v>61.93484833164811</v>
+      </c>
+      <c r="DY14" t="n">
+        <v>73.73931279261144</v>
+      </c>
+      <c r="DZ14" t="n">
+        <v>56.00360982410702</v>
+      </c>
+      <c r="EA14" t="n">
+        <v>59.00950150134857</v>
+      </c>
+      <c r="EB14" t="n">
+        <v>62.57803510870377</v>
+      </c>
+      <c r="EC14" t="n">
+        <v>56.71197189102454</v>
+      </c>
+      <c r="ED14" t="n">
+        <v>64.87463390602942</v>
+      </c>
+      <c r="EE14" t="n">
+        <v>58.04577600356904</v>
+      </c>
+      <c r="EF14" t="n">
+        <v>58.63259693577598</v>
+      </c>
+      <c r="EG14" t="n">
+        <v>61.71910044551651</v>
+      </c>
+      <c r="EH14" t="n">
         <v>55.77199911910693</v>
-      </c>
-      <c r="DP14" t="n">
-        <v>58.04577600356904</v>
-      </c>
-      <c r="DQ14" t="n">
-        <v>61.8487602337673</v>
-      </c>
-      <c r="DR14" t="n">
-        <v>63.52494797753565</v>
-      </c>
-      <c r="DS14" t="n">
-        <v>57.17305092357412</v>
-      </c>
-      <c r="DT14" t="n">
-        <v>59.66634940560481</v>
-      </c>
-      <c r="DU14" t="n">
-        <v>59.99268223964041</v>
-      </c>
-      <c r="DV14" t="n">
-        <v>59.75778773943138</v>
-      </c>
-      <c r="DW14" t="n">
-        <v>58.63259693577598</v>
-      </c>
-      <c r="DX14" t="n">
-        <v>57.36781868516248</v>
-      </c>
-      <c r="DY14" t="n">
-        <v>56.71197189102454</v>
-      </c>
-      <c r="DZ14" t="n">
-        <v>57.44158402253986</v>
-      </c>
-      <c r="EA14" t="n">
-        <v>58.79575680475884</v>
-      </c>
-      <c r="EB14" t="n">
-        <v>73.73931279261144</v>
-      </c>
-      <c r="EC14" t="n">
-        <v>76.06188777917092</v>
-      </c>
-      <c r="ED14" t="n">
-        <v>61.93484833164811</v>
-      </c>
-      <c r="EE14" t="n">
-        <v>62.88482941911205</v>
-      </c>
-      <c r="EF14" t="n">
-        <v>62.57803510870377</v>
-      </c>
-      <c r="EG14" t="n">
-        <v>67.79353601209482</v>
-      </c>
-      <c r="EH14" t="n">
-        <v>64.87463390602942</v>
       </c>
     </row>
     <row r="15">
@@ -6697,85 +6697,85 @@
         <v>0</v>
       </c>
       <c r="DH15" t="n">
-        <v>57.15884652507722</v>
+        <v>59.73494454693142</v>
       </c>
       <c r="DI15" t="n">
-        <v>56.35709811048363</v>
+        <v>76.91791720673886</v>
       </c>
       <c r="DJ15" t="n">
-        <v>59.73494454693142</v>
+        <v>57.76966266994827</v>
       </c>
       <c r="DK15" t="n">
-        <v>57.76966266994827</v>
+        <v>58.74785755305378</v>
       </c>
       <c r="DL15" t="n">
-        <v>62.37754527913582</v>
+        <v>60.90927571077065</v>
       </c>
       <c r="DM15" t="n">
-        <v>60.26130152282959</v>
+        <v>61.19346634923085</v>
       </c>
       <c r="DN15" t="n">
         <v>57.6921066124062</v>
       </c>
       <c r="DO15" t="n">
+        <v>60.70647694526323</v>
+      </c>
+      <c r="DP15" t="n">
+        <v>63.63045885227073</v>
+      </c>
+      <c r="DQ15" t="n">
+        <v>64.93969001590685</v>
+      </c>
+      <c r="DR15" t="n">
+        <v>58.67144064163804</v>
+      </c>
+      <c r="DS15" t="n">
+        <v>68.99224170052698</v>
+      </c>
+      <c r="DT15" t="n">
+        <v>58.98487188582335</v>
+      </c>
+      <c r="DU15" t="n">
+        <v>60.53571018064778</v>
+      </c>
+      <c r="DV15" t="n">
+        <v>56.35709811048363</v>
+      </c>
+      <c r="DW15" t="n">
+        <v>65.14756160726793</v>
+      </c>
+      <c r="DX15" t="n">
+        <v>64.02909170630596</v>
+      </c>
+      <c r="DY15" t="n">
+        <v>74.52072113692212</v>
+      </c>
+      <c r="DZ15" t="n">
+        <v>57.15884652507722</v>
+      </c>
+      <c r="EA15" t="n">
+        <v>60.26130152282959</v>
+      </c>
+      <c r="EB15" t="n">
+        <v>65.4775031754269</v>
+      </c>
+      <c r="EC15" t="n">
+        <v>58.37987453058606</v>
+      </c>
+      <c r="ED15" t="n">
+        <v>67.0674158860264</v>
+      </c>
+      <c r="EE15" t="n">
+        <v>59.90630590224153</v>
+      </c>
+      <c r="EF15" t="n">
+        <v>60.06984628466479</v>
+      </c>
+      <c r="EG15" t="n">
+        <v>62.37754527913582</v>
+      </c>
+      <c r="EH15" t="n">
         <v>57.68385633922989</v>
-      </c>
-      <c r="DP15" t="n">
-        <v>59.90630590224153</v>
-      </c>
-      <c r="DQ15" t="n">
-        <v>63.63045885227073</v>
-      </c>
-      <c r="DR15" t="n">
-        <v>65.14756160726793</v>
-      </c>
-      <c r="DS15" t="n">
-        <v>58.67144064163804</v>
-      </c>
-      <c r="DT15" t="n">
-        <v>60.70647694526323</v>
-      </c>
-      <c r="DU15" t="n">
-        <v>60.90927571077065</v>
-      </c>
-      <c r="DV15" t="n">
-        <v>61.19346634923085</v>
-      </c>
-      <c r="DW15" t="n">
-        <v>60.06984628466479</v>
-      </c>
-      <c r="DX15" t="n">
-        <v>58.74785755305378</v>
-      </c>
-      <c r="DY15" t="n">
-        <v>58.37987453058606</v>
-      </c>
-      <c r="DZ15" t="n">
-        <v>58.98487188582335</v>
-      </c>
-      <c r="EA15" t="n">
-        <v>60.53571018064778</v>
-      </c>
-      <c r="EB15" t="n">
-        <v>74.52072113692212</v>
-      </c>
-      <c r="EC15" t="n">
-        <v>76.91791720673886</v>
-      </c>
-      <c r="ED15" t="n">
-        <v>64.02909170630596</v>
-      </c>
-      <c r="EE15" t="n">
-        <v>64.93969001590685</v>
-      </c>
-      <c r="EF15" t="n">
-        <v>65.4775031754269</v>
-      </c>
-      <c r="EG15" t="n">
-        <v>68.99224170052698</v>
-      </c>
-      <c r="EH15" t="n">
-        <v>67.0674158860264</v>
       </c>
     </row>
     <row r="16">
@@ -7119,85 +7119,85 @@
         <v>0</v>
       </c>
       <c r="DH16" t="n">
-        <v>78.35421153410448</v>
+        <v>81.97978808916558</v>
       </c>
       <c r="DI16" t="n">
-        <v>77.30713756519641</v>
+        <v>105.6827240626393</v>
       </c>
       <c r="DJ16" t="n">
-        <v>81.97978808916558</v>
+        <v>78.38513693474127</v>
       </c>
       <c r="DK16" t="n">
-        <v>78.38513693474127</v>
+        <v>80.51372467147428</v>
       </c>
       <c r="DL16" t="n">
-        <v>84.77019281167532</v>
+        <v>84.65749640479333</v>
       </c>
       <c r="DM16" t="n">
-        <v>83.01998351458344</v>
+        <v>85.0377733737119</v>
       </c>
       <c r="DN16" t="n">
         <v>79.45912922565671</v>
       </c>
       <c r="DO16" t="n">
+        <v>83.85974106238878</v>
+      </c>
+      <c r="DP16" t="n">
+        <v>86.99996851001038</v>
+      </c>
+      <c r="DQ16" t="n">
+        <v>89.95891207159244</v>
+      </c>
+      <c r="DR16" t="n">
+        <v>80.90371882648135</v>
+      </c>
+      <c r="DS16" t="n">
+        <v>94.86597106538802</v>
+      </c>
+      <c r="DT16" t="n">
+        <v>80.847521007617</v>
+      </c>
+      <c r="DU16" t="n">
+        <v>82.83687894912343</v>
+      </c>
+      <c r="DV16" t="n">
+        <v>77.30713756519641</v>
+      </c>
+      <c r="DW16" t="n">
+        <v>90.02591328515803</v>
+      </c>
+      <c r="DX16" t="n">
+        <v>87.18496827623851</v>
+      </c>
+      <c r="DY16" t="n">
+        <v>101.8128174080095</v>
+      </c>
+      <c r="DZ16" t="n">
+        <v>78.35421153410448</v>
+      </c>
+      <c r="EA16" t="n">
+        <v>83.01998351458344</v>
+      </c>
+      <c r="EB16" t="n">
+        <v>89.76210878548343</v>
+      </c>
+      <c r="EC16" t="n">
+        <v>80.12559005790915</v>
+      </c>
+      <c r="ED16" t="n">
+        <v>93.78933765630147</v>
+      </c>
+      <c r="EE16" t="n">
+        <v>82.20843083646579</v>
+      </c>
+      <c r="EF16" t="n">
+        <v>82.58710507308602</v>
+      </c>
+      <c r="EG16" t="n">
+        <v>84.77019281167532</v>
+      </c>
+      <c r="EH16" t="n">
         <v>79.08567239905207</v>
-      </c>
-      <c r="DP16" t="n">
-        <v>82.20843083646579</v>
-      </c>
-      <c r="DQ16" t="n">
-        <v>86.99996851001038</v>
-      </c>
-      <c r="DR16" t="n">
-        <v>90.02591328515803</v>
-      </c>
-      <c r="DS16" t="n">
-        <v>80.90371882648135</v>
-      </c>
-      <c r="DT16" t="n">
-        <v>83.85974106238878</v>
-      </c>
-      <c r="DU16" t="n">
-        <v>84.65749640479333</v>
-      </c>
-      <c r="DV16" t="n">
-        <v>85.0377733737119</v>
-      </c>
-      <c r="DW16" t="n">
-        <v>82.58710507308602</v>
-      </c>
-      <c r="DX16" t="n">
-        <v>80.51372467147428</v>
-      </c>
-      <c r="DY16" t="n">
-        <v>80.12559005790915</v>
-      </c>
-      <c r="DZ16" t="n">
-        <v>80.847521007617</v>
-      </c>
-      <c r="EA16" t="n">
-        <v>82.83687894912343</v>
-      </c>
-      <c r="EB16" t="n">
-        <v>101.8128174080095</v>
-      </c>
-      <c r="EC16" t="n">
-        <v>105.6827240626393</v>
-      </c>
-      <c r="ED16" t="n">
-        <v>87.18496827623851</v>
-      </c>
-      <c r="EE16" t="n">
-        <v>89.95891207159244</v>
-      </c>
-      <c r="EF16" t="n">
-        <v>89.76210878548343</v>
-      </c>
-      <c r="EG16" t="n">
-        <v>94.86597106538802</v>
-      </c>
-      <c r="EH16" t="n">
-        <v>93.78933765630147</v>
       </c>
     </row>
     <row r="17">
@@ -7541,57 +7541,57 @@
         <v>171788.19</v>
       </c>
       <c r="DH17" t="inlineStr"/>
-      <c r="DI17" t="inlineStr"/>
+      <c r="DI17" t="n">
+        <v>35.25742016920846</v>
+      </c>
       <c r="DJ17" t="inlineStr"/>
-      <c r="DK17" t="inlineStr"/>
+      <c r="DK17" t="n">
+        <v>29.4380676012949</v>
+      </c>
       <c r="DL17" t="inlineStr"/>
-      <c r="DM17" t="n">
-        <v>35.74045648531961</v>
-      </c>
+      <c r="DM17" t="inlineStr"/>
       <c r="DN17" t="n">
         <v>26.72955917130101</v>
       </c>
-      <c r="DO17" t="n">
-        <v>26.76195751205169</v>
-      </c>
+      <c r="DO17" t="inlineStr"/>
       <c r="DP17" t="n">
+        <v>28.9073693778402</v>
+      </c>
+      <c r="DQ17" t="inlineStr"/>
+      <c r="DR17" t="inlineStr"/>
+      <c r="DS17" t="inlineStr"/>
+      <c r="DT17" t="n">
+        <v>27.30973631016685</v>
+      </c>
+      <c r="DU17" t="n">
+        <v>28.3913594280814</v>
+      </c>
+      <c r="DV17" t="inlineStr"/>
+      <c r="DW17" t="n">
+        <v>30.53827854681282</v>
+      </c>
+      <c r="DX17" t="inlineStr"/>
+      <c r="DY17" t="n">
+        <v>32.08966235036599</v>
+      </c>
+      <c r="DZ17" t="inlineStr"/>
+      <c r="EA17" t="n">
+        <v>35.74045648531961</v>
+      </c>
+      <c r="EB17" t="inlineStr"/>
+      <c r="EC17" t="n">
+        <v>27.40754485433868</v>
+      </c>
+      <c r="ED17" t="n">
+        <v>27.25028142978352</v>
+      </c>
+      <c r="EE17" t="n">
         <v>27.27461510269737</v>
       </c>
-      <c r="DQ17" t="n">
-        <v>28.9073693778402</v>
-      </c>
-      <c r="DR17" t="n">
-        <v>30.53827854681282</v>
-      </c>
-      <c r="DS17" t="inlineStr"/>
-      <c r="DT17" t="inlineStr"/>
-      <c r="DU17" t="inlineStr"/>
-      <c r="DV17" t="inlineStr"/>
-      <c r="DW17" t="inlineStr"/>
-      <c r="DX17" t="n">
-        <v>29.4380676012949</v>
-      </c>
-      <c r="DY17" t="n">
-        <v>27.40754485433868</v>
-      </c>
-      <c r="DZ17" t="n">
-        <v>27.30973631016685</v>
-      </c>
-      <c r="EA17" t="n">
-        <v>28.3913594280814</v>
-      </c>
-      <c r="EB17" t="n">
-        <v>32.08966235036599</v>
-      </c>
-      <c r="EC17" t="n">
-        <v>35.25742016920846</v>
-      </c>
-      <c r="ED17" t="inlineStr"/>
-      <c r="EE17" t="inlineStr"/>
       <c r="EF17" t="inlineStr"/>
       <c r="EG17" t="inlineStr"/>
       <c r="EH17" t="n">
-        <v>27.25028142978352</v>
+        <v>26.76195751205169</v>
       </c>
     </row>
     <row r="18">
@@ -7935,85 +7935,85 @@
         <v>1484587.35</v>
       </c>
       <c r="DH18" t="n">
-        <v>27.25296663367713</v>
+        <v>27.79788820199297</v>
       </c>
       <c r="DI18" t="n">
-        <v>28.34650926510049</v>
+        <v>33.62005808650301</v>
       </c>
       <c r="DJ18" t="n">
-        <v>27.79788820199297</v>
+        <v>28.14520540351069</v>
       </c>
       <c r="DK18" t="n">
-        <v>28.14520540351069</v>
+        <v>173.1624662711052</v>
       </c>
       <c r="DL18" t="n">
-        <v>27.09721459505023</v>
+        <v>30.09354657918454</v>
       </c>
       <c r="DM18" t="n">
-        <v>31.40112498033323</v>
+        <v>39.31172921475308</v>
       </c>
       <c r="DN18" t="n">
         <v>27.5734626917009</v>
       </c>
       <c r="DO18" t="n">
+        <v>27.79878922993512</v>
+      </c>
+      <c r="DP18" t="n">
+        <v>29.40769659845217</v>
+      </c>
+      <c r="DQ18" t="n">
+        <v>31.63913731434888</v>
+      </c>
+      <c r="DR18" t="n">
+        <v>26.93821802507497</v>
+      </c>
+      <c r="DS18" t="n">
+        <v>30.80360469258911</v>
+      </c>
+      <c r="DT18" t="n">
+        <v>603.8042103719745</v>
+      </c>
+      <c r="DU18" t="n">
+        <v>121.5220134114291</v>
+      </c>
+      <c r="DV18" t="n">
+        <v>28.34650926510049</v>
+      </c>
+      <c r="DW18" t="n">
+        <v>28.50667502947169</v>
+      </c>
+      <c r="DX18" t="n">
+        <v>29.17808256612772</v>
+      </c>
+      <c r="DY18" t="n">
+        <v>64.05786883711271</v>
+      </c>
+      <c r="DZ18" t="n">
+        <v>27.25296663367713</v>
+      </c>
+      <c r="EA18" t="n">
+        <v>31.40112498033323</v>
+      </c>
+      <c r="EB18" t="n">
+        <v>29.3348229396303</v>
+      </c>
+      <c r="EC18" t="n">
+        <v>209.9935635434452</v>
+      </c>
+      <c r="ED18" t="n">
+        <v>31.80548703627648</v>
+      </c>
+      <c r="EE18" t="n">
+        <v>27.01653144235938</v>
+      </c>
+      <c r="EF18" t="n">
+        <v>43.60736775976022</v>
+      </c>
+      <c r="EG18" t="n">
+        <v>27.09721459505023</v>
+      </c>
+      <c r="EH18" t="n">
         <v>27.02819296267267</v>
-      </c>
-      <c r="DP18" t="n">
-        <v>27.01653144235938</v>
-      </c>
-      <c r="DQ18" t="n">
-        <v>29.40769659845217</v>
-      </c>
-      <c r="DR18" t="n">
-        <v>28.50667502947169</v>
-      </c>
-      <c r="DS18" t="n">
-        <v>26.93821802507497</v>
-      </c>
-      <c r="DT18" t="n">
-        <v>27.79878922993512</v>
-      </c>
-      <c r="DU18" t="n">
-        <v>30.09354657918454</v>
-      </c>
-      <c r="DV18" t="n">
-        <v>39.31172921475308</v>
-      </c>
-      <c r="DW18" t="n">
-        <v>43.60736775976022</v>
-      </c>
-      <c r="DX18" t="n">
-        <v>173.1624662711052</v>
-      </c>
-      <c r="DY18" t="n">
-        <v>209.9935635434452</v>
-      </c>
-      <c r="DZ18" t="n">
-        <v>603.8042103719745</v>
-      </c>
-      <c r="EA18" t="n">
-        <v>121.5220134114291</v>
-      </c>
-      <c r="EB18" t="n">
-        <v>64.05786883711271</v>
-      </c>
-      <c r="EC18" t="n">
-        <v>33.62005808650301</v>
-      </c>
-      <c r="ED18" t="n">
-        <v>29.17808256612772</v>
-      </c>
-      <c r="EE18" t="n">
-        <v>31.63913731434888</v>
-      </c>
-      <c r="EF18" t="n">
-        <v>29.3348229396303</v>
-      </c>
-      <c r="EG18" t="n">
-        <v>30.80360469258911</v>
-      </c>
-      <c r="EH18" t="n">
-        <v>31.80548703627648</v>
       </c>
     </row>
     <row r="19">
@@ -8357,85 +8357,85 @@
         <v>838017.7482499999</v>
       </c>
       <c r="DH19" t="n">
-        <v>36.83978162049415</v>
+        <v>32.3457571745727</v>
       </c>
       <c r="DI19" t="n">
-        <v>29.72606277190012</v>
+        <v>127.0832177195242</v>
       </c>
       <c r="DJ19" t="n">
-        <v>32.3457571745727</v>
+        <v>38.70152244175095</v>
       </c>
       <c r="DK19" t="n">
-        <v>38.70152244175095</v>
+        <v>70.93751962027575</v>
       </c>
       <c r="DL19" t="n">
-        <v>47.84385945160348</v>
+        <v>33.0959078351318</v>
       </c>
       <c r="DM19" t="n">
-        <v>102.5423275965083</v>
+        <v>28.92819928331788</v>
       </c>
       <c r="DN19" t="n">
         <v>108.219778962169</v>
       </c>
       <c r="DO19" t="n">
+        <v>32.11791868195326</v>
+      </c>
+      <c r="DP19" t="n">
+        <v>120.6452948725401</v>
+      </c>
+      <c r="DQ19" t="n">
+        <v>40.64148176092863</v>
+      </c>
+      <c r="DR19" t="n">
+        <v>31.90366416533729</v>
+      </c>
+      <c r="DS19" t="n">
+        <v>30.59353762638498</v>
+      </c>
+      <c r="DT19" t="n">
+        <v>91.26219083555907</v>
+      </c>
+      <c r="DU19" t="n">
+        <v>102.6297166402755</v>
+      </c>
+      <c r="DV19" t="n">
+        <v>29.72606277190012</v>
+      </c>
+      <c r="DW19" t="n">
+        <v>66.91807019780506</v>
+      </c>
+      <c r="DX19" t="n">
+        <v>49.41525192935512</v>
+      </c>
+      <c r="DY19" t="n">
+        <v>112.1258696048909</v>
+      </c>
+      <c r="DZ19" t="n">
+        <v>36.83978162049415</v>
+      </c>
+      <c r="EA19" t="n">
+        <v>102.5423275965083</v>
+      </c>
+      <c r="EB19" t="n">
+        <v>29.35918294499168</v>
+      </c>
+      <c r="EC19" t="n">
+        <v>98.28714422124368</v>
+      </c>
+      <c r="ED19" t="n">
+        <v>82.28202593024162</v>
+      </c>
+      <c r="EE19" t="n">
+        <v>120.2996929128205</v>
+      </c>
+      <c r="EF19" t="n">
+        <v>45.42535907065567</v>
+      </c>
+      <c r="EG19" t="n">
+        <v>47.84385945160348</v>
+      </c>
+      <c r="EH19" t="n">
         <v>118.3823485562315</v>
-      </c>
-      <c r="DP19" t="n">
-        <v>120.2996929128205</v>
-      </c>
-      <c r="DQ19" t="n">
-        <v>120.6452948725401</v>
-      </c>
-      <c r="DR19" t="n">
-        <v>66.91807019780506</v>
-      </c>
-      <c r="DS19" t="n">
-        <v>31.90366416533729</v>
-      </c>
-      <c r="DT19" t="n">
-        <v>32.11791868195326</v>
-      </c>
-      <c r="DU19" t="n">
-        <v>33.0959078351318</v>
-      </c>
-      <c r="DV19" t="n">
-        <v>28.92819928331788</v>
-      </c>
-      <c r="DW19" t="n">
-        <v>45.42535907065567</v>
-      </c>
-      <c r="DX19" t="n">
-        <v>70.93751962027575</v>
-      </c>
-      <c r="DY19" t="n">
-        <v>98.28714422124368</v>
-      </c>
-      <c r="DZ19" t="n">
-        <v>91.26219083555907</v>
-      </c>
-      <c r="EA19" t="n">
-        <v>102.6297166402755</v>
-      </c>
-      <c r="EB19" t="n">
-        <v>112.1258696048909</v>
-      </c>
-      <c r="EC19" t="n">
-        <v>127.0832177195242</v>
-      </c>
-      <c r="ED19" t="n">
-        <v>49.41525192935512</v>
-      </c>
-      <c r="EE19" t="n">
-        <v>40.64148176092863</v>
-      </c>
-      <c r="EF19" t="n">
-        <v>29.35918294499168</v>
-      </c>
-      <c r="EG19" t="n">
-        <v>30.59353762638498</v>
-      </c>
-      <c r="EH19" t="n">
-        <v>82.28202593024162</v>
       </c>
     </row>
     <row r="20">
@@ -8779,85 +8779,85 @@
         <v>62818.86442072635</v>
       </c>
       <c r="DH20" t="n">
-        <v>22.29250444247615</v>
+        <v>22.89028549940023</v>
       </c>
       <c r="DI20" t="n">
-        <v>26.22735335375174</v>
+        <v>34.64349509728233</v>
       </c>
       <c r="DJ20" t="n">
-        <v>22.89028549940023</v>
+        <v>23.65454455920921</v>
       </c>
       <c r="DK20" t="n">
-        <v>23.65454455920921</v>
+        <v>26.14905501638095</v>
       </c>
       <c r="DL20" t="n">
-        <v>30.1708360024585</v>
+        <v>22.04695501067436</v>
       </c>
       <c r="DM20" t="n">
-        <v>36.87429227940986</v>
+        <v>20.07271126473092</v>
       </c>
       <c r="DN20" t="n">
         <v>50.8966574253265</v>
       </c>
       <c r="DO20" t="n">
+        <v>17.16014810226786</v>
+      </c>
+      <c r="DP20" t="n">
+        <v>26.72655393540958</v>
+      </c>
+      <c r="DQ20" t="n">
+        <v>26.66641743360386</v>
+      </c>
+      <c r="DR20" t="n">
+        <v>24.27873693362852</v>
+      </c>
+      <c r="DS20" t="n">
+        <v>39.3218275273512</v>
+      </c>
+      <c r="DT20" t="n">
+        <v>36.51304476434448</v>
+      </c>
+      <c r="DU20" t="n">
+        <v>35.0381358863949</v>
+      </c>
+      <c r="DV20" t="n">
+        <v>26.22735335375174</v>
+      </c>
+      <c r="DW20" t="n">
+        <v>26.72432700771543</v>
+      </c>
+      <c r="DX20" t="n">
+        <v>28.51074914838717</v>
+      </c>
+      <c r="DY20" t="n">
+        <v>40.98408870169738</v>
+      </c>
+      <c r="DZ20" t="n">
+        <v>22.29250444247615</v>
+      </c>
+      <c r="EA20" t="n">
+        <v>36.87429227940986</v>
+      </c>
+      <c r="EB20" t="n">
+        <v>33.46687722427194</v>
+      </c>
+      <c r="EC20" t="n">
+        <v>43.22873510554857</v>
+      </c>
+      <c r="ED20" t="n">
+        <v>46.42711019258128</v>
+      </c>
+      <c r="EE20" t="n">
+        <v>40.90532915841398</v>
+      </c>
+      <c r="EF20" t="n">
+        <v>22.45760993175253</v>
+      </c>
+      <c r="EG20" t="n">
+        <v>30.1708360024585</v>
+      </c>
+      <c r="EH20" t="n">
         <v>60.1862685598288</v>
-      </c>
-      <c r="DP20" t="n">
-        <v>40.90532915841398</v>
-      </c>
-      <c r="DQ20" t="n">
-        <v>26.72655393540958</v>
-      </c>
-      <c r="DR20" t="n">
-        <v>26.72432700771543</v>
-      </c>
-      <c r="DS20" t="n">
-        <v>24.27873693362852</v>
-      </c>
-      <c r="DT20" t="n">
-        <v>17.16014810226786</v>
-      </c>
-      <c r="DU20" t="n">
-        <v>22.04695501067436</v>
-      </c>
-      <c r="DV20" t="n">
-        <v>20.07271126473092</v>
-      </c>
-      <c r="DW20" t="n">
-        <v>22.45760993175253</v>
-      </c>
-      <c r="DX20" t="n">
-        <v>26.14905501638095</v>
-      </c>
-      <c r="DY20" t="n">
-        <v>43.22873510554857</v>
-      </c>
-      <c r="DZ20" t="n">
-        <v>36.51304476434448</v>
-      </c>
-      <c r="EA20" t="n">
-        <v>35.0381358863949</v>
-      </c>
-      <c r="EB20" t="n">
-        <v>40.98408870169738</v>
-      </c>
-      <c r="EC20" t="n">
-        <v>34.64349509728233</v>
-      </c>
-      <c r="ED20" t="n">
-        <v>28.51074914838717</v>
-      </c>
-      <c r="EE20" t="n">
-        <v>26.66641743360386</v>
-      </c>
-      <c r="EF20" t="n">
-        <v>33.46687722427194</v>
-      </c>
-      <c r="EG20" t="n">
-        <v>39.3218275273512</v>
-      </c>
-      <c r="EH20" t="n">
-        <v>46.42711019258128</v>
       </c>
     </row>
     <row r="21">
@@ -9569,85 +9569,85 @@
         <v>70747.5405</v>
       </c>
       <c r="DH22" t="n">
-        <v>88.37099318817663</v>
+        <v>76.5407793777669</v>
       </c>
       <c r="DI22" t="n">
-        <v>55.57976908497889</v>
+        <v>79.5506216266815</v>
       </c>
       <c r="DJ22" t="n">
-        <v>76.5407793777669</v>
+        <v>92.95124022977681</v>
       </c>
       <c r="DK22" t="n">
-        <v>92.95124022977681</v>
+        <v>61.05912075706064</v>
       </c>
       <c r="DL22" t="n">
-        <v>93.66305161087558</v>
+        <v>41.42850429959852</v>
       </c>
       <c r="DM22" t="n">
-        <v>99.44186557233247</v>
+        <v>41.2728146393837</v>
       </c>
       <c r="DN22" t="n">
         <v>96.37099236291152</v>
       </c>
       <c r="DO22" t="n">
+        <v>87.78047531744186</v>
+      </c>
+      <c r="DP22" t="n">
+        <v>101.1304610352375</v>
+      </c>
+      <c r="DQ22" t="n">
+        <v>64.51790616256756</v>
+      </c>
+      <c r="DR22" t="n">
+        <v>99.46324439538741</v>
+      </c>
+      <c r="DS22" t="n">
+        <v>34.72900708818397</v>
+      </c>
+      <c r="DT22" t="n">
+        <v>69.7111605070185</v>
+      </c>
+      <c r="DU22" t="n">
+        <v>80.95602165890193</v>
+      </c>
+      <c r="DV22" t="n">
+        <v>55.57976908497889</v>
+      </c>
+      <c r="DW22" t="n">
+        <v>93.59687581098807</v>
+      </c>
+      <c r="DX22" t="n">
+        <v>72.69550209608823</v>
+      </c>
+      <c r="DY22" t="n">
+        <v>80.20254145547119</v>
+      </c>
+      <c r="DZ22" t="n">
+        <v>88.37099318817663</v>
+      </c>
+      <c r="EA22" t="n">
+        <v>99.44186557233247</v>
+      </c>
+      <c r="EB22" t="n">
+        <v>34.22818214770538</v>
+      </c>
+      <c r="EC22" t="n">
+        <v>64.6385706169839</v>
+      </c>
+      <c r="ED22" t="n">
+        <v>59.14095177811726</v>
+      </c>
+      <c r="EE22" t="n">
+        <v>111.16608885221</v>
+      </c>
+      <c r="EF22" t="n">
+        <v>57.38263183412995</v>
+      </c>
+      <c r="EG22" t="n">
+        <v>93.66305161087558</v>
+      </c>
+      <c r="EH22" t="n">
         <v>99.80298329717016</v>
-      </c>
-      <c r="DP22" t="n">
-        <v>111.16608885221</v>
-      </c>
-      <c r="DQ22" t="n">
-        <v>101.1304610352375</v>
-      </c>
-      <c r="DR22" t="n">
-        <v>93.59687581098807</v>
-      </c>
-      <c r="DS22" t="n">
-        <v>99.46324439538741</v>
-      </c>
-      <c r="DT22" t="n">
-        <v>87.78047531744186</v>
-      </c>
-      <c r="DU22" t="n">
-        <v>41.42850429959852</v>
-      </c>
-      <c r="DV22" t="n">
-        <v>41.2728146393837</v>
-      </c>
-      <c r="DW22" t="n">
-        <v>57.38263183412995</v>
-      </c>
-      <c r="DX22" t="n">
-        <v>61.05912075706064</v>
-      </c>
-      <c r="DY22" t="n">
-        <v>64.6385706169839</v>
-      </c>
-      <c r="DZ22" t="n">
-        <v>69.7111605070185</v>
-      </c>
-      <c r="EA22" t="n">
-        <v>80.95602165890193</v>
-      </c>
-      <c r="EB22" t="n">
-        <v>80.20254145547119</v>
-      </c>
-      <c r="EC22" t="n">
-        <v>79.5506216266815</v>
-      </c>
-      <c r="ED22" t="n">
-        <v>72.69550209608823</v>
-      </c>
-      <c r="EE22" t="n">
-        <v>64.51790616256756</v>
-      </c>
-      <c r="EF22" t="n">
-        <v>34.22818214770538</v>
-      </c>
-      <c r="EG22" t="n">
-        <v>34.72900708818397</v>
-      </c>
-      <c r="EH22" t="n">
-        <v>59.14095177811726</v>
       </c>
     </row>
     <row r="23">
@@ -9991,85 +9991,85 @@
         <v>206891.7435</v>
       </c>
       <c r="DH23" t="n">
-        <v>69.99258543452723</v>
+        <v>37.37250555517036</v>
       </c>
       <c r="DI23" t="n">
-        <v>40.31174746582619</v>
+        <v>50.64726594314652</v>
       </c>
       <c r="DJ23" t="n">
-        <v>37.37250555517036</v>
+        <v>42.86427867066229</v>
       </c>
       <c r="DK23" t="n">
-        <v>42.86427867066229</v>
+        <v>44.65518816724775</v>
       </c>
       <c r="DL23" t="n">
-        <v>52.85740483086861</v>
+        <v>33.94366123499809</v>
       </c>
       <c r="DM23" t="n">
-        <v>43.09646987986092</v>
+        <v>34.70049777681257</v>
       </c>
       <c r="DN23" t="n">
         <v>36.1723966677321</v>
       </c>
       <c r="DO23" t="n">
+        <v>46.24949522366455</v>
+      </c>
+      <c r="DP23" t="n">
+        <v>42.13845127040579</v>
+      </c>
+      <c r="DQ23" t="n">
+        <v>34.0363218097357</v>
+      </c>
+      <c r="DR23" t="n">
+        <v>31.78949279878156</v>
+      </c>
+      <c r="DS23" t="n">
+        <v>35.46515939930589</v>
+      </c>
+      <c r="DT23" t="n">
+        <v>34.09365265324117</v>
+      </c>
+      <c r="DU23" t="n">
+        <v>37.85872343607663</v>
+      </c>
+      <c r="DV23" t="n">
+        <v>40.31174746582619</v>
+      </c>
+      <c r="DW23" t="n">
+        <v>32.36295904407247</v>
+      </c>
+      <c r="DX23" t="n">
+        <v>34.79741453749293</v>
+      </c>
+      <c r="DY23" t="n">
+        <v>43.0543448827163</v>
+      </c>
+      <c r="DZ23" t="n">
+        <v>69.99258543452723</v>
+      </c>
+      <c r="EA23" t="n">
+        <v>43.09646987986092</v>
+      </c>
+      <c r="EB23" t="n">
+        <v>35.32969358463499</v>
+      </c>
+      <c r="EC23" t="n">
+        <v>37.58776705019416</v>
+      </c>
+      <c r="ED23" t="n">
+        <v>34.7452214059386</v>
+      </c>
+      <c r="EE23" t="n">
+        <v>92.13190483861075</v>
+      </c>
+      <c r="EF23" t="n">
+        <v>48.13474889624125</v>
+      </c>
+      <c r="EG23" t="n">
+        <v>52.85740483086861</v>
+      </c>
+      <c r="EH23" t="n">
         <v>40.55022788405461</v>
-      </c>
-      <c r="DP23" t="n">
-        <v>92.13190483861075</v>
-      </c>
-      <c r="DQ23" t="n">
-        <v>42.13845127040579</v>
-      </c>
-      <c r="DR23" t="n">
-        <v>32.36295904407247</v>
-      </c>
-      <c r="DS23" t="n">
-        <v>31.78949279878156</v>
-      </c>
-      <c r="DT23" t="n">
-        <v>46.24949522366455</v>
-      </c>
-      <c r="DU23" t="n">
-        <v>33.94366123499809</v>
-      </c>
-      <c r="DV23" t="n">
-        <v>34.70049777681257</v>
-      </c>
-      <c r="DW23" t="n">
-        <v>48.13474889624125</v>
-      </c>
-      <c r="DX23" t="n">
-        <v>44.65518816724775</v>
-      </c>
-      <c r="DY23" t="n">
-        <v>37.58776705019416</v>
-      </c>
-      <c r="DZ23" t="n">
-        <v>34.09365265324117</v>
-      </c>
-      <c r="EA23" t="n">
-        <v>37.85872343607663</v>
-      </c>
-      <c r="EB23" t="n">
-        <v>43.0543448827163</v>
-      </c>
-      <c r="EC23" t="n">
-        <v>50.64726594314652</v>
-      </c>
-      <c r="ED23" t="n">
-        <v>34.79741453749293</v>
-      </c>
-      <c r="EE23" t="n">
-        <v>34.0363218097357</v>
-      </c>
-      <c r="EF23" t="n">
-        <v>35.32969358463499</v>
-      </c>
-      <c r="EG23" t="n">
-        <v>35.46515939930589</v>
-      </c>
-      <c r="EH23" t="n">
-        <v>34.7452214059386</v>
       </c>
     </row>
     <row r="24">
@@ -10781,85 +10781,85 @@
         <v>1143104.0335</v>
       </c>
       <c r="DH25" t="n">
-        <v>74.03156404210984</v>
+        <v>131.3982943097305</v>
       </c>
       <c r="DI25" t="n">
-        <v>133.4846964296934</v>
+        <v>83.428111063288</v>
       </c>
       <c r="DJ25" t="n">
-        <v>131.3982943097305</v>
+        <v>109.8764772639442</v>
       </c>
       <c r="DK25" t="n">
-        <v>109.8764772639442</v>
+        <v>126.9944687715585</v>
       </c>
       <c r="DL25" t="n">
-        <v>109.1808998224668</v>
+        <v>203.3614615263488</v>
       </c>
       <c r="DM25" t="n">
-        <v>93.06168476304369</v>
+        <v>183.6215011397552</v>
       </c>
       <c r="DN25" t="n">
         <v>75.08953461817148</v>
       </c>
       <c r="DO25" t="n">
+        <v>142.7578897404362</v>
+      </c>
+      <c r="DP25" t="n">
+        <v>83.37092455858513</v>
+      </c>
+      <c r="DQ25" t="n">
+        <v>110.2278460720957</v>
+      </c>
+      <c r="DR25" t="n">
+        <v>100.8463274026924</v>
+      </c>
+      <c r="DS25" t="n">
+        <v>143.5084052218959</v>
+      </c>
+      <c r="DT25" t="n">
+        <v>81.98509385353178</v>
+      </c>
+      <c r="DU25" t="n">
+        <v>85.08956425605848</v>
+      </c>
+      <c r="DV25" t="n">
+        <v>133.4846964296934</v>
+      </c>
+      <c r="DW25" t="n">
+        <v>89.80774688156983</v>
+      </c>
+      <c r="DX25" t="n">
+        <v>90.86247766644519</v>
+      </c>
+      <c r="DY25" t="n">
+        <v>89.30106428167055</v>
+      </c>
+      <c r="DZ25" t="n">
+        <v>74.03156404210984</v>
+      </c>
+      <c r="EA25" t="n">
+        <v>93.06168476304369</v>
+      </c>
+      <c r="EB25" t="n">
+        <v>124.389042433222</v>
+      </c>
+      <c r="EC25" t="n">
+        <v>92.42356350130224</v>
+      </c>
+      <c r="ED25" t="n">
+        <v>112.3922225007854</v>
+      </c>
+      <c r="EE25" t="n">
+        <v>98.09386343467901</v>
+      </c>
+      <c r="EF25" t="n">
+        <v>160.5713250491854</v>
+      </c>
+      <c r="EG25" t="n">
+        <v>109.1808998224668</v>
+      </c>
+      <c r="EH25" t="n">
         <v>78.97111840143101</v>
-      </c>
-      <c r="DP25" t="n">
-        <v>98.09386343467901</v>
-      </c>
-      <c r="DQ25" t="n">
-        <v>83.37092455858513</v>
-      </c>
-      <c r="DR25" t="n">
-        <v>89.80774688156983</v>
-      </c>
-      <c r="DS25" t="n">
-        <v>100.8463274026924</v>
-      </c>
-      <c r="DT25" t="n">
-        <v>142.7578897404362</v>
-      </c>
-      <c r="DU25" t="n">
-        <v>203.3614615263488</v>
-      </c>
-      <c r="DV25" t="n">
-        <v>183.6215011397552</v>
-      </c>
-      <c r="DW25" t="n">
-        <v>160.5713250491854</v>
-      </c>
-      <c r="DX25" t="n">
-        <v>126.9944687715585</v>
-      </c>
-      <c r="DY25" t="n">
-        <v>92.42356350130224</v>
-      </c>
-      <c r="DZ25" t="n">
-        <v>81.98509385353178</v>
-      </c>
-      <c r="EA25" t="n">
-        <v>85.08956425605848</v>
-      </c>
-      <c r="EB25" t="n">
-        <v>89.30106428167055</v>
-      </c>
-      <c r="EC25" t="n">
-        <v>83.428111063288</v>
-      </c>
-      <c r="ED25" t="n">
-        <v>90.86247766644519</v>
-      </c>
-      <c r="EE25" t="n">
-        <v>110.2278460720957</v>
-      </c>
-      <c r="EF25" t="n">
-        <v>124.389042433222</v>
-      </c>
-      <c r="EG25" t="n">
-        <v>143.5084052218959</v>
-      </c>
-      <c r="EH25" t="n">
-        <v>112.3922225007854</v>
       </c>
     </row>
     <row r="26">
@@ -11203,85 +11203,85 @@
         <v>0</v>
       </c>
       <c r="DH26" t="n">
-        <v>15.90122642728468</v>
+        <v>16.32536950226842</v>
       </c>
       <c r="DI26" t="n">
-        <v>15.66154909453935</v>
+        <v>20.27098038974561</v>
       </c>
       <c r="DJ26" t="n">
-        <v>16.32536950226842</v>
+        <v>16.81808009533631</v>
       </c>
       <c r="DK26" t="n">
-        <v>16.81808009533631</v>
+        <v>14.99917743749428</v>
       </c>
       <c r="DL26" t="n">
-        <v>17.17102997565696</v>
+        <v>16.54542523668618</v>
       </c>
       <c r="DM26" t="n">
-        <v>16.77490934683216</v>
+        <v>15.52605343677438</v>
       </c>
       <c r="DN26" t="n">
         <v>15.77350947795784</v>
       </c>
       <c r="DO26" t="n">
+        <v>16.5825670729863</v>
+      </c>
+      <c r="DP26" t="n">
+        <v>16.75178529644628</v>
+      </c>
+      <c r="DQ26" t="n">
+        <v>16.08349547846713</v>
+      </c>
+      <c r="DR26" t="n">
+        <v>15.13667934806808</v>
+      </c>
+      <c r="DS26" t="n">
+        <v>16.2545098338756</v>
+      </c>
+      <c r="DT26" t="n">
+        <v>15.23179928485978</v>
+      </c>
+      <c r="DU26" t="n">
+        <v>15.26468777775109</v>
+      </c>
+      <c r="DV26" t="n">
+        <v>15.66154909453935</v>
+      </c>
+      <c r="DW26" t="n">
+        <v>17.39202513659103</v>
+      </c>
+      <c r="DX26" t="n">
+        <v>15.96345014463347</v>
+      </c>
+      <c r="DY26" t="n">
+        <v>18.88838376822923</v>
+      </c>
+      <c r="DZ26" t="n">
+        <v>15.90122642728468</v>
+      </c>
+      <c r="EA26" t="n">
+        <v>16.77490934683216</v>
+      </c>
+      <c r="EB26" t="n">
+        <v>15.45073277953128</v>
+      </c>
+      <c r="EC26" t="n">
+        <v>15.09481121768056</v>
+      </c>
+      <c r="ED26" t="n">
+        <v>15.56296114090651</v>
+      </c>
+      <c r="EE26" t="n">
+        <v>15.91541613592217</v>
+      </c>
+      <c r="EF26" t="n">
+        <v>15.24566840242382</v>
+      </c>
+      <c r="EG26" t="n">
+        <v>17.17102997565696</v>
+      </c>
+      <c r="EH26" t="n">
         <v>16.08915589991005</v>
-      </c>
-      <c r="DP26" t="n">
-        <v>15.91541613592217</v>
-      </c>
-      <c r="DQ26" t="n">
-        <v>16.75178529644628</v>
-      </c>
-      <c r="DR26" t="n">
-        <v>17.39202513659103</v>
-      </c>
-      <c r="DS26" t="n">
-        <v>15.13667934806808</v>
-      </c>
-      <c r="DT26" t="n">
-        <v>16.5825670729863</v>
-      </c>
-      <c r="DU26" t="n">
-        <v>16.54542523668618</v>
-      </c>
-      <c r="DV26" t="n">
-        <v>15.52605343677438</v>
-      </c>
-      <c r="DW26" t="n">
-        <v>15.24566840242382</v>
-      </c>
-      <c r="DX26" t="n">
-        <v>14.99917743749428</v>
-      </c>
-      <c r="DY26" t="n">
-        <v>15.09481121768056</v>
-      </c>
-      <c r="DZ26" t="n">
-        <v>15.23179928485978</v>
-      </c>
-      <c r="EA26" t="n">
-        <v>15.26468777775109</v>
-      </c>
-      <c r="EB26" t="n">
-        <v>18.88838376822923</v>
-      </c>
-      <c r="EC26" t="n">
-        <v>20.27098038974561</v>
-      </c>
-      <c r="ED26" t="n">
-        <v>15.96345014463347</v>
-      </c>
-      <c r="EE26" t="n">
-        <v>16.08349547846713</v>
-      </c>
-      <c r="EF26" t="n">
-        <v>15.45073277953128</v>
-      </c>
-      <c r="EG26" t="n">
-        <v>16.2545098338756</v>
-      </c>
-      <c r="EH26" t="n">
-        <v>15.56296114090651</v>
       </c>
     </row>
     <row r="27">
@@ -11625,85 +11625,85 @@
         <v>0</v>
       </c>
       <c r="DH27" t="n">
-        <v>54.87465181058496</v>
+        <v>55.98146998401223</v>
       </c>
       <c r="DI27" t="n">
-        <v>53.4801792637507</v>
+        <v>77.48831970106858</v>
       </c>
       <c r="DJ27" t="n">
-        <v>55.98146998401223</v>
+        <v>57.48020624834992</v>
       </c>
       <c r="DK27" t="n">
-        <v>57.48020624834992</v>
+        <v>54.12853594698573</v>
       </c>
       <c r="DL27" t="n">
-        <v>58.10542163871727</v>
+        <v>59.88784074568635</v>
       </c>
       <c r="DM27" t="n">
-        <v>57.91661462694973</v>
+        <v>54.38284764492342</v>
       </c>
       <c r="DN27" t="n">
         <v>54.55368382934967</v>
       </c>
       <c r="DO27" t="n">
+        <v>59.8854752445404</v>
+      </c>
+      <c r="DP27" t="n">
+        <v>58.65675911158898</v>
+      </c>
+      <c r="DQ27" t="n">
+        <v>62.65192089938969</v>
+      </c>
+      <c r="DR27" t="n">
+        <v>53.2182895588319</v>
+      </c>
+      <c r="DS27" t="n">
+        <v>65.71326701427365</v>
+      </c>
+      <c r="DT27" t="n">
+        <v>55.28701268487756</v>
+      </c>
+      <c r="DU27" t="n">
+        <v>56.09024349644569</v>
+      </c>
+      <c r="DV27" t="n">
+        <v>53.4801792637507</v>
+      </c>
+      <c r="DW27" t="n">
+        <v>62.38648932309523</v>
+      </c>
+      <c r="DX27" t="n">
+        <v>61.22478036767654</v>
+      </c>
+      <c r="DY27" t="n">
+        <v>70.38327699735368</v>
+      </c>
+      <c r="DZ27" t="n">
+        <v>54.87465181058496</v>
+      </c>
+      <c r="EA27" t="n">
+        <v>57.91661462694973</v>
+      </c>
+      <c r="EB27" t="n">
+        <v>63.2502276355765</v>
+      </c>
+      <c r="EC27" t="n">
+        <v>54.77867130669218</v>
+      </c>
+      <c r="ED27" t="n">
+        <v>67.81815117773618</v>
+      </c>
+      <c r="EE27" t="n">
+        <v>55.29176198922335</v>
+      </c>
+      <c r="EF27" t="n">
+        <v>53.80279507881036</v>
+      </c>
+      <c r="EG27" t="n">
+        <v>58.10542163871727</v>
+      </c>
+      <c r="EH27" t="n">
         <v>56.06307360000268</v>
-      </c>
-      <c r="DP27" t="n">
-        <v>55.29176198922335</v>
-      </c>
-      <c r="DQ27" t="n">
-        <v>58.65675911158898</v>
-      </c>
-      <c r="DR27" t="n">
-        <v>62.38648932309523</v>
-      </c>
-      <c r="DS27" t="n">
-        <v>53.2182895588319</v>
-      </c>
-      <c r="DT27" t="n">
-        <v>59.8854752445404</v>
-      </c>
-      <c r="DU27" t="n">
-        <v>59.88784074568635</v>
-      </c>
-      <c r="DV27" t="n">
-        <v>54.38284764492342</v>
-      </c>
-      <c r="DW27" t="n">
-        <v>53.80279507881036</v>
-      </c>
-      <c r="DX27" t="n">
-        <v>54.12853594698573</v>
-      </c>
-      <c r="DY27" t="n">
-        <v>54.77867130669218</v>
-      </c>
-      <c r="DZ27" t="n">
-        <v>55.28701268487756</v>
-      </c>
-      <c r="EA27" t="n">
-        <v>56.09024349644569</v>
-      </c>
-      <c r="EB27" t="n">
-        <v>70.38327699735368</v>
-      </c>
-      <c r="EC27" t="n">
-        <v>77.48831970106858</v>
-      </c>
-      <c r="ED27" t="n">
-        <v>61.22478036767654</v>
-      </c>
-      <c r="EE27" t="n">
-        <v>62.65192089938969</v>
-      </c>
-      <c r="EF27" t="n">
-        <v>63.2502276355765</v>
-      </c>
-      <c r="EG27" t="n">
-        <v>65.71326701427365</v>
-      </c>
-      <c r="EH27" t="n">
-        <v>67.81815117773618</v>
       </c>
     </row>
     <row r="28">
@@ -12039,76 +12039,76 @@
       </c>
       <c r="DG28" t="inlineStr"/>
       <c r="DH28" t="n">
-        <v>42.85855017738326</v>
+        <v>42.20499745887413</v>
       </c>
       <c r="DI28" t="n">
-        <v>41.79458697309089</v>
+        <v>31.66790693038362</v>
       </c>
       <c r="DJ28" t="n">
-        <v>42.20499745887413</v>
+        <v>44.73326777639497</v>
       </c>
       <c r="DK28" t="n">
-        <v>44.73326777639497</v>
+        <v>33.52337248992878</v>
       </c>
       <c r="DL28" t="n">
-        <v>44.3710117355583</v>
+        <v>49.20466116700855</v>
       </c>
       <c r="DM28" t="n">
-        <v>44.7154216467962</v>
+        <v>37.33295709344855</v>
       </c>
       <c r="DN28" t="n">
         <v>39.1244441081697</v>
       </c>
       <c r="DO28" t="n">
+        <v>45.00243064117155</v>
+      </c>
+      <c r="DP28" t="n">
+        <v>48.02740328128537</v>
+      </c>
+      <c r="DQ28" t="inlineStr"/>
+      <c r="DR28" t="n">
+        <v>43.30832054795079</v>
+      </c>
+      <c r="DS28" t="inlineStr"/>
+      <c r="DT28" t="n">
+        <v>25.12959380336694</v>
+      </c>
+      <c r="DU28" t="n">
+        <v>25.39600288563904</v>
+      </c>
+      <c r="DV28" t="n">
+        <v>41.79458697309089</v>
+      </c>
+      <c r="DW28" t="n">
+        <v>48.84463477716572</v>
+      </c>
+      <c r="DX28" t="inlineStr"/>
+      <c r="DY28" t="n">
+        <v>28.9702738768039</v>
+      </c>
+      <c r="DZ28" t="n">
+        <v>42.85855017738326</v>
+      </c>
+      <c r="EA28" t="n">
+        <v>44.7154216467962</v>
+      </c>
+      <c r="EB28" t="inlineStr"/>
+      <c r="EC28" t="n">
+        <v>24.96165034696997</v>
+      </c>
+      <c r="ED28" t="inlineStr"/>
+      <c r="EE28" t="n">
+        <v>45.59663174473005</v>
+      </c>
+      <c r="EF28" t="n">
+        <v>45.1163845903937</v>
+      </c>
+      <c r="EG28" t="n">
+        <v>44.3710117355583</v>
+      </c>
+      <c r="EH28" t="n">
         <v>43.43053423300059</v>
       </c>
-      <c r="DP28" t="n">
-        <v>45.59663174473005</v>
-      </c>
-      <c r="DQ28" t="n">
-        <v>48.02740328128537</v>
-      </c>
-      <c r="DR28" t="n">
-        <v>48.84463477716572</v>
-      </c>
-      <c r="DS28" t="n">
-        <v>43.30832054795079</v>
-      </c>
-      <c r="DT28" t="n">
-        <v>45.00243064117155</v>
-      </c>
-      <c r="DU28" t="n">
-        <v>49.20466116700855</v>
-      </c>
-      <c r="DV28" t="n">
-        <v>37.33295709344855</v>
-      </c>
-      <c r="DW28" t="n">
-        <v>45.1163845903937</v>
-      </c>
-      <c r="DX28" t="n">
-        <v>33.52337248992878</v>
-      </c>
-      <c r="DY28" t="n">
-        <v>24.96165034696997</v>
-      </c>
-      <c r="DZ28" t="n">
-        <v>25.12959380336694</v>
-      </c>
-      <c r="EA28" t="n">
-        <v>25.39600288563904</v>
-      </c>
-      <c r="EB28" t="n">
-        <v>28.9702738768039</v>
-      </c>
-      <c r="EC28" t="n">
-        <v>31.66790693038362</v>
-      </c>
-      <c r="ED28" t="inlineStr"/>
-      <c r="EE28" t="inlineStr"/>
-      <c r="EF28" t="inlineStr"/>
-      <c r="EG28" t="inlineStr"/>
-      <c r="EH28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -12121,7 +12121,11 @@
           <t>ENDE GENERACION</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="n">
@@ -12607,85 +12611,85 @@
         <v>19709.8785</v>
       </c>
       <c r="DH30" t="n">
-        <v>46.50589189825867</v>
+        <v>33.79235985212488</v>
       </c>
       <c r="DI30" t="n">
-        <v>31.63621355386378</v>
+        <v>102.1435917406867</v>
       </c>
       <c r="DJ30" t="n">
-        <v>33.79235985212488</v>
+        <v>34.77754892666115</v>
       </c>
       <c r="DK30" t="n">
-        <v>34.77754892666115</v>
+        <v>54.95889987171466</v>
       </c>
       <c r="DL30" t="n">
-        <v>40.66176206706465</v>
+        <v>40.24824028400101</v>
       </c>
       <c r="DM30" t="n">
-        <v>56.31004835884149</v>
+        <v>30.77477762140746</v>
       </c>
       <c r="DN30" t="n">
         <v>61.80204910278623</v>
       </c>
       <c r="DO30" t="n">
+        <v>52.66431249362397</v>
+      </c>
+      <c r="DP30" t="n">
+        <v>82.32355394411437</v>
+      </c>
+      <c r="DQ30" t="n">
+        <v>54.28750630201747</v>
+      </c>
+      <c r="DR30" t="n">
+        <v>57.54590474266804</v>
+      </c>
+      <c r="DS30" t="n">
+        <v>35.05457363157684</v>
+      </c>
+      <c r="DT30" t="n">
+        <v>82.15779936200197</v>
+      </c>
+      <c r="DU30" t="n">
+        <v>96.88639181017327</v>
+      </c>
+      <c r="DV30" t="n">
+        <v>31.63621355386378</v>
+      </c>
+      <c r="DW30" t="n">
+        <v>70.34349948552793</v>
+      </c>
+      <c r="DX30" t="n">
+        <v>78.85837014221606</v>
+      </c>
+      <c r="DY30" t="n">
+        <v>109.7454886194953</v>
+      </c>
+      <c r="DZ30" t="n">
+        <v>46.50589189825867</v>
+      </c>
+      <c r="EA30" t="n">
+        <v>56.31004835884149</v>
+      </c>
+      <c r="EB30" t="n">
+        <v>35.97588933609331</v>
+      </c>
+      <c r="EC30" t="n">
+        <v>71.66250140611687</v>
+      </c>
+      <c r="ED30" t="n">
+        <v>43.77337691523098</v>
+      </c>
+      <c r="EE30" t="n">
+        <v>75.21573162860641</v>
+      </c>
+      <c r="EF30" t="n">
+        <v>38.1084594115192</v>
+      </c>
+      <c r="EG30" t="n">
+        <v>40.66176206706465</v>
+      </c>
+      <c r="EH30" t="n">
         <v>70.84330684774673</v>
-      </c>
-      <c r="DP30" t="n">
-        <v>75.21573162860641</v>
-      </c>
-      <c r="DQ30" t="n">
-        <v>82.32355394411437</v>
-      </c>
-      <c r="DR30" t="n">
-        <v>70.34349948552793</v>
-      </c>
-      <c r="DS30" t="n">
-        <v>57.54590474266804</v>
-      </c>
-      <c r="DT30" t="n">
-        <v>52.66431249362397</v>
-      </c>
-      <c r="DU30" t="n">
-        <v>40.24824028400101</v>
-      </c>
-      <c r="DV30" t="n">
-        <v>30.77477762140746</v>
-      </c>
-      <c r="DW30" t="n">
-        <v>38.1084594115192</v>
-      </c>
-      <c r="DX30" t="n">
-        <v>54.95889987171466</v>
-      </c>
-      <c r="DY30" t="n">
-        <v>71.66250140611687</v>
-      </c>
-      <c r="DZ30" t="n">
-        <v>82.15779936200197</v>
-      </c>
-      <c r="EA30" t="n">
-        <v>96.88639181017327</v>
-      </c>
-      <c r="EB30" t="n">
-        <v>109.7454886194953</v>
-      </c>
-      <c r="EC30" t="n">
-        <v>102.1435917406867</v>
-      </c>
-      <c r="ED30" t="n">
-        <v>78.85837014221606</v>
-      </c>
-      <c r="EE30" t="n">
-        <v>54.28750630201747</v>
-      </c>
-      <c r="EF30" t="n">
-        <v>35.97588933609331</v>
-      </c>
-      <c r="EG30" t="n">
-        <v>35.05457363157684</v>
-      </c>
-      <c r="EH30" t="n">
-        <v>43.77337691523098</v>
       </c>
     </row>
     <row r="31">
@@ -12699,7 +12703,11 @@
           <t>ENDE GENERACION</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="n">
@@ -12855,7 +12863,11 @@
           <t>ENDE GENERACION</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="n">
@@ -13341,85 +13353,85 @@
         <v>78323.83375000001</v>
       </c>
       <c r="DH33" t="n">
-        <v>183.1498513319893</v>
+        <v>29.2306023715003</v>
       </c>
       <c r="DI33" t="n">
-        <v>35.18433713867534</v>
+        <v>92.13436579430474</v>
       </c>
       <c r="DJ33" t="n">
-        <v>29.2306023715003</v>
+        <v>38.42033617996444</v>
       </c>
       <c r="DK33" t="n">
-        <v>38.42033617996444</v>
+        <v>69.8243738653304</v>
       </c>
       <c r="DL33" t="n">
-        <v>82.89309947556538</v>
+        <v>30.54343585001464</v>
       </c>
       <c r="DM33" t="n">
-        <v>129.1487446801946</v>
+        <v>28.20291380693357</v>
       </c>
       <c r="DN33" t="n">
         <v>133.0193109294235</v>
       </c>
       <c r="DO33" t="n">
+        <v>32.4468331442438</v>
+      </c>
+      <c r="DP33" t="n">
+        <v>243.4518773340106</v>
+      </c>
+      <c r="DQ33" t="n">
+        <v>63.05108372781795</v>
+      </c>
+      <c r="DR33" t="n">
+        <v>98.3891811077402</v>
+      </c>
+      <c r="DS33" t="n">
+        <v>35.265825315253</v>
+      </c>
+      <c r="DT33" t="n">
+        <v>171.2642269805718</v>
+      </c>
+      <c r="DU33" t="n">
+        <v>133.5914645827848</v>
+      </c>
+      <c r="DV33" t="n">
+        <v>35.18433713867534</v>
+      </c>
+      <c r="DW33" t="n">
+        <v>172.4441907702119</v>
+      </c>
+      <c r="DX33" t="n">
+        <v>47.16737942097112</v>
+      </c>
+      <c r="DY33" t="n">
+        <v>186.0054395642619</v>
+      </c>
+      <c r="DZ33" t="n">
+        <v>183.1498513319893</v>
+      </c>
+      <c r="EA33" t="n">
+        <v>129.1487446801946</v>
+      </c>
+      <c r="EB33" t="n">
+        <v>30.24421587360824</v>
+      </c>
+      <c r="EC33" t="n">
+        <v>123.7011733975139</v>
+      </c>
+      <c r="ED33" t="n">
+        <v>127.9952778068762</v>
+      </c>
+      <c r="EE33" t="n">
+        <v>187.2899990888014</v>
+      </c>
+      <c r="EF33" t="n">
+        <v>31.84884779101516</v>
+      </c>
+      <c r="EG33" t="n">
+        <v>82.89309947556538</v>
+      </c>
+      <c r="EH33" t="n">
         <v>177.5169456989311</v>
-      </c>
-      <c r="DP33" t="n">
-        <v>187.2899990888014</v>
-      </c>
-      <c r="DQ33" t="n">
-        <v>243.4518773340106</v>
-      </c>
-      <c r="DR33" t="n">
-        <v>172.4441907702119</v>
-      </c>
-      <c r="DS33" t="n">
-        <v>98.3891811077402</v>
-      </c>
-      <c r="DT33" t="n">
-        <v>32.4468331442438</v>
-      </c>
-      <c r="DU33" t="n">
-        <v>30.54343585001464</v>
-      </c>
-      <c r="DV33" t="n">
-        <v>28.20291380693357</v>
-      </c>
-      <c r="DW33" t="n">
-        <v>31.84884779101516</v>
-      </c>
-      <c r="DX33" t="n">
-        <v>69.8243738653304</v>
-      </c>
-      <c r="DY33" t="n">
-        <v>123.7011733975139</v>
-      </c>
-      <c r="DZ33" t="n">
-        <v>171.2642269805718</v>
-      </c>
-      <c r="EA33" t="n">
-        <v>133.5914645827848</v>
-      </c>
-      <c r="EB33" t="n">
-        <v>186.0054395642619</v>
-      </c>
-      <c r="EC33" t="n">
-        <v>92.13436579430474</v>
-      </c>
-      <c r="ED33" t="n">
-        <v>47.16737942097112</v>
-      </c>
-      <c r="EE33" t="n">
-        <v>63.05108372781795</v>
-      </c>
-      <c r="EF33" t="n">
-        <v>30.24421587360824</v>
-      </c>
-      <c r="EG33" t="n">
-        <v>35.265825315253</v>
-      </c>
-      <c r="EH33" t="n">
-        <v>127.9952778068762</v>
       </c>
     </row>
     <row r="34">
@@ -13763,85 +13775,85 @@
         <v>526825.3365</v>
       </c>
       <c r="DH34" t="n">
-        <v>50.95386455748168</v>
+        <v>45.25530550978625</v>
       </c>
       <c r="DI34" t="n">
-        <v>42.16894724129989</v>
+        <v>49.34970417452364</v>
       </c>
       <c r="DJ34" t="n">
-        <v>45.25530550978625</v>
+        <v>44.88067783497432</v>
       </c>
       <c r="DK34" t="n">
-        <v>44.88067783497432</v>
+        <v>32.77907819700069</v>
       </c>
       <c r="DL34" t="n">
-        <v>61.08406931123566</v>
+        <v>34.00784250550562</v>
       </c>
       <c r="DM34" t="n">
-        <v>59.24559716042921</v>
+        <v>27.94436065454308</v>
       </c>
       <c r="DN34" t="n">
         <v>59.51730898347285</v>
       </c>
       <c r="DO34" t="n">
+        <v>34.45250523894621</v>
+      </c>
+      <c r="DP34" t="n">
+        <v>46.55516593356111</v>
+      </c>
+      <c r="DQ34" t="n">
+        <v>32.71205122375284</v>
+      </c>
+      <c r="DR34" t="n">
+        <v>28.98190966753128</v>
+      </c>
+      <c r="DS34" t="n">
+        <v>34.94523550206061</v>
+      </c>
+      <c r="DT34" t="n">
+        <v>38.75633922614567</v>
+      </c>
+      <c r="DU34" t="n">
+        <v>45.61041751002049</v>
+      </c>
+      <c r="DV34" t="n">
+        <v>42.16894724129989</v>
+      </c>
+      <c r="DW34" t="n">
+        <v>37.25064115130812</v>
+      </c>
+      <c r="DX34" t="n">
+        <v>44.92134003884966</v>
+      </c>
+      <c r="DY34" t="n">
+        <v>47.00599394835503</v>
+      </c>
+      <c r="DZ34" t="n">
+        <v>50.95386455748168</v>
+      </c>
+      <c r="EA34" t="n">
+        <v>59.24559716042921</v>
+      </c>
+      <c r="EB34" t="n">
+        <v>29.30569407796402</v>
+      </c>
+      <c r="EC34" t="n">
+        <v>36.53923498359479</v>
+      </c>
+      <c r="ED34" t="n">
+        <v>34.57397859182687</v>
+      </c>
+      <c r="EE34" t="n">
+        <v>57.53405658587145</v>
+      </c>
+      <c r="EF34" t="n">
+        <v>29.06636410591276</v>
+      </c>
+      <c r="EG34" t="n">
+        <v>61.08406931123566</v>
+      </c>
+      <c r="EH34" t="n">
         <v>65.54338503486778</v>
-      </c>
-      <c r="DP34" t="n">
-        <v>57.53405658587145</v>
-      </c>
-      <c r="DQ34" t="n">
-        <v>46.55516593356111</v>
-      </c>
-      <c r="DR34" t="n">
-        <v>37.25064115130812</v>
-      </c>
-      <c r="DS34" t="n">
-        <v>28.98190966753128</v>
-      </c>
-      <c r="DT34" t="n">
-        <v>34.45250523894621</v>
-      </c>
-      <c r="DU34" t="n">
-        <v>34.00784250550562</v>
-      </c>
-      <c r="DV34" t="n">
-        <v>27.94436065454308</v>
-      </c>
-      <c r="DW34" t="n">
-        <v>29.06636410591276</v>
-      </c>
-      <c r="DX34" t="n">
-        <v>32.77907819700069</v>
-      </c>
-      <c r="DY34" t="n">
-        <v>36.53923498359479</v>
-      </c>
-      <c r="DZ34" t="n">
-        <v>38.75633922614567</v>
-      </c>
-      <c r="EA34" t="n">
-        <v>45.61041751002049</v>
-      </c>
-      <c r="EB34" t="n">
-        <v>47.00599394835503</v>
-      </c>
-      <c r="EC34" t="n">
-        <v>49.34970417452364</v>
-      </c>
-      <c r="ED34" t="n">
-        <v>44.92134003884966</v>
-      </c>
-      <c r="EE34" t="n">
-        <v>32.71205122375284</v>
-      </c>
-      <c r="EF34" t="n">
-        <v>29.30569407796402</v>
-      </c>
-      <c r="EG34" t="n">
-        <v>34.94523550206061</v>
-      </c>
-      <c r="EH34" t="n">
-        <v>34.57397859182687</v>
       </c>
     </row>
     <row r="35">
@@ -14185,85 +14197,85 @@
         <v>664960.6305</v>
       </c>
       <c r="DH35" t="n">
-        <v>54.00688243397617</v>
+        <v>47.60177990022714</v>
       </c>
       <c r="DI35" t="n">
-        <v>44.692113447739</v>
+        <v>51.89239542000757</v>
       </c>
       <c r="DJ35" t="n">
-        <v>47.60177990022714</v>
+        <v>47.1829372489567</v>
       </c>
       <c r="DK35" t="n">
-        <v>47.1829372489567</v>
+        <v>34.13890008358752</v>
       </c>
       <c r="DL35" t="n">
-        <v>64.92407681466607</v>
+        <v>35.92445335680902</v>
       </c>
       <c r="DM35" t="n">
-        <v>63.30786468830421</v>
+        <v>29.06907473496362</v>
       </c>
       <c r="DN35" t="n">
         <v>63.19283752290114</v>
       </c>
       <c r="DO35" t="n">
+        <v>36.02736178233364</v>
+      </c>
+      <c r="DP35" t="n">
+        <v>49.51195064924867</v>
+      </c>
+      <c r="DQ35" t="n">
+        <v>34.12598787205851</v>
+      </c>
+      <c r="DR35" t="n">
+        <v>30.19045518917249</v>
+      </c>
+      <c r="DS35" t="n">
+        <v>36.61330406033309</v>
+      </c>
+      <c r="DT35" t="n">
+        <v>40.70295225611648</v>
+      </c>
+      <c r="DU35" t="n">
+        <v>47.79462332276475</v>
+      </c>
+      <c r="DV35" t="n">
+        <v>44.692113447739</v>
+      </c>
+      <c r="DW35" t="n">
+        <v>39.02148329418184</v>
+      </c>
+      <c r="DX35" t="n">
+        <v>47.50272603962956</v>
+      </c>
+      <c r="DY35" t="n">
+        <v>49.82660432348481</v>
+      </c>
+      <c r="DZ35" t="n">
+        <v>54.00688243397617</v>
+      </c>
+      <c r="EA35" t="n">
+        <v>63.30786468830421</v>
+      </c>
+      <c r="EB35" t="n">
+        <v>30.72972070808314</v>
+      </c>
+      <c r="EC35" t="n">
+        <v>38.65881705015274</v>
+      </c>
+      <c r="ED35" t="n">
+        <v>36.29281448229294</v>
+      </c>
+      <c r="EE35" t="n">
+        <v>60.74292584998749</v>
+      </c>
+      <c r="EF35" t="n">
+        <v>30.34260763635253</v>
+      </c>
+      <c r="EG35" t="n">
+        <v>64.92407681466607</v>
+      </c>
+      <c r="EH35" t="n">
         <v>69.26254259341196</v>
-      </c>
-      <c r="DP35" t="n">
-        <v>60.74292584998749</v>
-      </c>
-      <c r="DQ35" t="n">
-        <v>49.51195064924867</v>
-      </c>
-      <c r="DR35" t="n">
-        <v>39.02148329418184</v>
-      </c>
-      <c r="DS35" t="n">
-        <v>30.19045518917249</v>
-      </c>
-      <c r="DT35" t="n">
-        <v>36.02736178233364</v>
-      </c>
-      <c r="DU35" t="n">
-        <v>35.92445335680902</v>
-      </c>
-      <c r="DV35" t="n">
-        <v>29.06907473496362</v>
-      </c>
-      <c r="DW35" t="n">
-        <v>30.34260763635253</v>
-      </c>
-      <c r="DX35" t="n">
-        <v>34.13890008358752</v>
-      </c>
-      <c r="DY35" t="n">
-        <v>38.65881705015274</v>
-      </c>
-      <c r="DZ35" t="n">
-        <v>40.70295225611648</v>
-      </c>
-      <c r="EA35" t="n">
-        <v>47.79462332276475</v>
-      </c>
-      <c r="EB35" t="n">
-        <v>49.82660432348481</v>
-      </c>
-      <c r="EC35" t="n">
-        <v>51.89239542000757</v>
-      </c>
-      <c r="ED35" t="n">
-        <v>47.50272603962956</v>
-      </c>
-      <c r="EE35" t="n">
-        <v>34.12598787205851</v>
-      </c>
-      <c r="EF35" t="n">
-        <v>30.72972070808314</v>
-      </c>
-      <c r="EG35" t="n">
-        <v>36.61330406033309</v>
-      </c>
-      <c r="EH35" t="n">
-        <v>36.29281448229294</v>
       </c>
     </row>
     <row r="36">
@@ -14277,7 +14289,11 @@
           <t>ENDE GENERACION</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr"/>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="n">
@@ -14763,72 +14779,72 @@
         <v>0</v>
       </c>
       <c r="DH37" t="n">
-        <v>21.51902513518386</v>
-      </c>
-      <c r="DI37" t="inlineStr"/>
+        <v>20.83904046232418</v>
+      </c>
+      <c r="DI37" t="n">
+        <v>24.98185340666741</v>
+      </c>
       <c r="DJ37" t="n">
-        <v>20.83904046232418</v>
+        <v>21.04027883566297</v>
       </c>
       <c r="DK37" t="n">
-        <v>21.04027883566297</v>
+        <v>25.70552656718418</v>
       </c>
       <c r="DL37" t="n">
-        <v>23.24781583716615</v>
-      </c>
-      <c r="DM37" t="inlineStr"/>
+        <v>23.6480036838491</v>
+      </c>
+      <c r="DM37" t="n">
+        <v>23.70700572699445</v>
+      </c>
       <c r="DN37" t="n">
         <v>27.44552852261236</v>
       </c>
       <c r="DO37" t="n">
+        <v>26.64379774537349</v>
+      </c>
+      <c r="DP37" t="n">
+        <v>24.96314793230875</v>
+      </c>
+      <c r="DQ37" t="n">
+        <v>25.9720999259864</v>
+      </c>
+      <c r="DR37" t="n">
+        <v>26.67101771872942</v>
+      </c>
+      <c r="DS37" t="n">
+        <v>25.19086023602631</v>
+      </c>
+      <c r="DT37" t="inlineStr"/>
+      <c r="DU37" t="n">
+        <v>210.784831155495</v>
+      </c>
+      <c r="DV37" t="inlineStr"/>
+      <c r="DW37" t="n">
+        <v>29.45576222728974</v>
+      </c>
+      <c r="DX37" t="inlineStr"/>
+      <c r="DY37" t="n">
+        <v>25.23704734789544</v>
+      </c>
+      <c r="DZ37" t="n">
+        <v>21.51902513518386</v>
+      </c>
+      <c r="EA37" t="inlineStr"/>
+      <c r="EB37" t="n">
+        <v>25.79723548774233</v>
+      </c>
+      <c r="EC37" t="inlineStr"/>
+      <c r="ED37" t="inlineStr"/>
+      <c r="EE37" t="inlineStr"/>
+      <c r="EF37" t="n">
+        <v>23.82887976788317</v>
+      </c>
+      <c r="EG37" t="n">
+        <v>23.24781583716615</v>
+      </c>
+      <c r="EH37" t="n">
         <v>32.6346506429576</v>
       </c>
-      <c r="DP37" t="inlineStr"/>
-      <c r="DQ37" t="n">
-        <v>24.96314793230875</v>
-      </c>
-      <c r="DR37" t="n">
-        <v>29.45576222728974</v>
-      </c>
-      <c r="DS37" t="n">
-        <v>26.67101771872942</v>
-      </c>
-      <c r="DT37" t="n">
-        <v>26.64379774537349</v>
-      </c>
-      <c r="DU37" t="n">
-        <v>23.6480036838491</v>
-      </c>
-      <c r="DV37" t="n">
-        <v>23.70700572699445</v>
-      </c>
-      <c r="DW37" t="n">
-        <v>23.82887976788317</v>
-      </c>
-      <c r="DX37" t="n">
-        <v>25.70552656718418</v>
-      </c>
-      <c r="DY37" t="inlineStr"/>
-      <c r="DZ37" t="inlineStr"/>
-      <c r="EA37" t="n">
-        <v>210.784831155495</v>
-      </c>
-      <c r="EB37" t="n">
-        <v>25.23704734789544</v>
-      </c>
-      <c r="EC37" t="n">
-        <v>24.98185340666741</v>
-      </c>
-      <c r="ED37" t="inlineStr"/>
-      <c r="EE37" t="n">
-        <v>25.9720999259864</v>
-      </c>
-      <c r="EF37" t="n">
-        <v>25.79723548774233</v>
-      </c>
-      <c r="EG37" t="n">
-        <v>25.19086023602631</v>
-      </c>
-      <c r="EH37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -15347,42 +15363,42 @@
         <v>0</v>
       </c>
       <c r="DH39" t="inlineStr"/>
-      <c r="DI39" t="inlineStr"/>
+      <c r="DI39" t="n">
+        <v>34.85041669964225</v>
+      </c>
       <c r="DJ39" t="inlineStr"/>
       <c r="DK39" t="inlineStr"/>
       <c r="DL39" t="inlineStr"/>
       <c r="DM39" t="inlineStr"/>
       <c r="DN39" t="inlineStr"/>
-      <c r="DO39" t="n">
-        <v>29.276202935197</v>
-      </c>
-      <c r="DP39" t="n">
-        <v>29.99253616444193</v>
-      </c>
+      <c r="DO39" t="inlineStr"/>
+      <c r="DP39" t="inlineStr"/>
       <c r="DQ39" t="inlineStr"/>
       <c r="DR39" t="inlineStr"/>
       <c r="DS39" t="inlineStr"/>
       <c r="DT39" t="inlineStr"/>
-      <c r="DU39" t="inlineStr"/>
+      <c r="DU39" t="n">
+        <v>29.77074543356832</v>
+      </c>
       <c r="DV39" t="inlineStr"/>
       <c r="DW39" t="inlineStr"/>
       <c r="DX39" t="inlineStr"/>
-      <c r="DY39" t="inlineStr"/>
+      <c r="DY39" t="n">
+        <v>32.41085685142915</v>
+      </c>
       <c r="DZ39" t="inlineStr"/>
-      <c r="EA39" t="n">
-        <v>29.77074543356832</v>
-      </c>
-      <c r="EB39" t="n">
-        <v>32.41085685142915</v>
-      </c>
-      <c r="EC39" t="n">
-        <v>34.85041669964225</v>
-      </c>
+      <c r="EA39" t="inlineStr"/>
+      <c r="EB39" t="inlineStr"/>
+      <c r="EC39" t="inlineStr"/>
       <c r="ED39" t="inlineStr"/>
-      <c r="EE39" t="inlineStr"/>
+      <c r="EE39" t="n">
+        <v>29.99253616444193</v>
+      </c>
       <c r="EF39" t="inlineStr"/>
       <c r="EG39" t="inlineStr"/>
-      <c r="EH39" t="inlineStr"/>
+      <c r="EH39" t="n">
+        <v>29.276202935197</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -15725,7 +15741,9 @@
         <v>104049.33</v>
       </c>
       <c r="DH40" t="inlineStr"/>
-      <c r="DI40" t="inlineStr"/>
+      <c r="DI40" t="n">
+        <v>34.6467571991866</v>
+      </c>
       <c r="DJ40" t="inlineStr"/>
       <c r="DK40" t="inlineStr"/>
       <c r="DL40" t="inlineStr"/>
@@ -15733,45 +15751,43 @@
       <c r="DN40" t="n">
         <v>29.59643610640058</v>
       </c>
-      <c r="DO40" t="n">
-        <v>28.28425885751584</v>
-      </c>
+      <c r="DO40" t="inlineStr"/>
       <c r="DP40" t="n">
-        <v>29.14896657993646</v>
-      </c>
-      <c r="DQ40" t="n">
         <v>30.05805477864697</v>
       </c>
-      <c r="DR40" t="n">
+      <c r="DQ40" t="inlineStr"/>
+      <c r="DR40" t="inlineStr"/>
+      <c r="DS40" t="inlineStr"/>
+      <c r="DT40" t="n">
+        <v>28.96980174068775</v>
+      </c>
+      <c r="DU40" t="n">
+        <v>29.31217141923422</v>
+      </c>
+      <c r="DV40" t="inlineStr"/>
+      <c r="DW40" t="n">
         <v>29.68388941621605</v>
       </c>
-      <c r="DS40" t="inlineStr"/>
-      <c r="DT40" t="inlineStr"/>
-      <c r="DU40" t="inlineStr"/>
-      <c r="DV40" t="inlineStr"/>
-      <c r="DW40" t="inlineStr"/>
       <c r="DX40" t="inlineStr"/>
       <c r="DY40" t="n">
+        <v>33.15870995104898</v>
+      </c>
+      <c r="DZ40" t="inlineStr"/>
+      <c r="EA40" t="inlineStr"/>
+      <c r="EB40" t="inlineStr"/>
+      <c r="EC40" t="n">
         <v>29.30675734253598</v>
       </c>
-      <c r="DZ40" t="n">
-        <v>28.96980174068775</v>
-      </c>
-      <c r="EA40" t="n">
-        <v>29.31217141923422</v>
-      </c>
-      <c r="EB40" t="n">
-        <v>33.15870995104898</v>
-      </c>
-      <c r="EC40" t="n">
-        <v>34.6467571991866</v>
-      </c>
-      <c r="ED40" t="inlineStr"/>
-      <c r="EE40" t="inlineStr"/>
+      <c r="ED40" t="n">
+        <v>30.54654654371722</v>
+      </c>
+      <c r="EE40" t="n">
+        <v>29.14896657993646</v>
+      </c>
       <c r="EF40" t="inlineStr"/>
       <c r="EG40" t="inlineStr"/>
       <c r="EH40" t="n">
-        <v>30.54654654371722</v>
+        <v>28.28425885751584</v>
       </c>
     </row>
     <row r="41">
@@ -16115,85 +16131,85 @@
         <v>845308.46325</v>
       </c>
       <c r="DH41" t="n">
-        <v>79.14964995406967</v>
+        <v>209.218677735756</v>
       </c>
       <c r="DI41" t="n">
-        <v>184.6742589422481</v>
+        <v>42.29910055750423</v>
       </c>
       <c r="DJ41" t="n">
-        <v>209.218677735756</v>
+        <v>113.316736393968</v>
       </c>
       <c r="DK41" t="n">
-        <v>113.316736393968</v>
+        <v>33.11467646152695</v>
       </c>
       <c r="DL41" t="n">
-        <v>112.3557316445036</v>
+        <v>47.44253598244694</v>
       </c>
       <c r="DM41" t="n">
-        <v>60.40678457383105</v>
+        <v>28.89204898255377</v>
       </c>
       <c r="DN41" t="n">
         <v>53.32357965811186</v>
       </c>
       <c r="DO41" t="n">
+        <v>68.96949311241461</v>
+      </c>
+      <c r="DP41" t="n">
+        <v>46.47646313806546</v>
+      </c>
+      <c r="DQ41" t="n">
+        <v>39.32621558756026</v>
+      </c>
+      <c r="DR41" t="n">
+        <v>32.7363029356967</v>
+      </c>
+      <c r="DS41" t="n">
+        <v>48.80546862265204</v>
+      </c>
+      <c r="DT41" t="n">
+        <v>33.8168995972804</v>
+      </c>
+      <c r="DU41" t="n">
+        <v>38.1966685609769</v>
+      </c>
+      <c r="DV41" t="n">
+        <v>184.6742589422481</v>
+      </c>
+      <c r="DW41" t="n">
+        <v>43.12205146948526</v>
+      </c>
+      <c r="DX41" t="n">
+        <v>45.9412910269071</v>
+      </c>
+      <c r="DY41" t="n">
+        <v>39.73129720866189</v>
+      </c>
+      <c r="DZ41" t="n">
+        <v>79.14964995406967</v>
+      </c>
+      <c r="EA41" t="n">
+        <v>60.40678457383105</v>
+      </c>
+      <c r="EB41" t="n">
+        <v>38.98101305438478</v>
+      </c>
+      <c r="EC41" t="n">
+        <v>33.26096140540955</v>
+      </c>
+      <c r="ED41" t="n">
+        <v>30.59454386827415</v>
+      </c>
+      <c r="EE41" t="n">
+        <v>51.44827617135794</v>
+      </c>
+      <c r="EF41" t="n">
+        <v>30.54550344684563</v>
+      </c>
+      <c r="EG41" t="n">
+        <v>112.3557316445036</v>
+      </c>
+      <c r="EH41" t="n">
         <v>49.25903143206968</v>
-      </c>
-      <c r="DP41" t="n">
-        <v>51.44827617135794</v>
-      </c>
-      <c r="DQ41" t="n">
-        <v>46.47646313806546</v>
-      </c>
-      <c r="DR41" t="n">
-        <v>43.12205146948526</v>
-      </c>
-      <c r="DS41" t="n">
-        <v>32.7363029356967</v>
-      </c>
-      <c r="DT41" t="n">
-        <v>68.96949311241461</v>
-      </c>
-      <c r="DU41" t="n">
-        <v>47.44253598244694</v>
-      </c>
-      <c r="DV41" t="n">
-        <v>28.89204898255377</v>
-      </c>
-      <c r="DW41" t="n">
-        <v>30.54550344684563</v>
-      </c>
-      <c r="DX41" t="n">
-        <v>33.11467646152695</v>
-      </c>
-      <c r="DY41" t="n">
-        <v>33.26096140540955</v>
-      </c>
-      <c r="DZ41" t="n">
-        <v>33.8168995972804</v>
-      </c>
-      <c r="EA41" t="n">
-        <v>38.1966685609769</v>
-      </c>
-      <c r="EB41" t="n">
-        <v>39.73129720866189</v>
-      </c>
-      <c r="EC41" t="n">
-        <v>42.29910055750423</v>
-      </c>
-      <c r="ED41" t="n">
-        <v>45.9412910269071</v>
-      </c>
-      <c r="EE41" t="n">
-        <v>39.32621558756026</v>
-      </c>
-      <c r="EF41" t="n">
-        <v>38.98101305438478</v>
-      </c>
-      <c r="EG41" t="n">
-        <v>48.80546862265204</v>
-      </c>
-      <c r="EH41" t="n">
-        <v>30.59454386827415</v>
       </c>
     </row>
     <row r="42">
@@ -16537,85 +16553,85 @@
         <v>0</v>
       </c>
       <c r="DH42" t="n">
-        <v>51.714451082964</v>
+        <v>53.85386549215347</v>
       </c>
       <c r="DI42" t="n">
-        <v>49.75489278345417</v>
+        <v>65.36693034912744</v>
       </c>
       <c r="DJ42" t="n">
-        <v>53.85386549215347</v>
+        <v>52.07787556602706</v>
       </c>
       <c r="DK42" t="n">
-        <v>52.07787556602706</v>
+        <v>50.8277124201076</v>
       </c>
       <c r="DL42" t="n">
-        <v>54.41235009143887</v>
+        <v>53.61237412091314</v>
       </c>
       <c r="DM42" t="n">
-        <v>55.98379916045716</v>
+        <v>51.37257100924343</v>
       </c>
       <c r="DN42" t="n">
         <v>51.83229191207158</v>
       </c>
       <c r="DO42" t="n">
+        <v>53.88614428288363</v>
+      </c>
+      <c r="DP42" t="n">
+        <v>56.48465183952614</v>
+      </c>
+      <c r="DQ42" t="n">
+        <v>58.05879351413334</v>
+      </c>
+      <c r="DR42" t="n">
+        <v>49.83279365780958</v>
+      </c>
+      <c r="DS42" t="n">
+        <v>56.38251177574104</v>
+      </c>
+      <c r="DT42" t="n">
+        <v>51.86218133406767</v>
+      </c>
+      <c r="DU42" t="n">
+        <v>53.15559539689821</v>
+      </c>
+      <c r="DV42" t="n">
+        <v>49.75489278345417</v>
+      </c>
+      <c r="DW42" t="n">
+        <v>56.60642794632711</v>
+      </c>
+      <c r="DX42" t="n">
+        <v>55.17325698678211</v>
+      </c>
+      <c r="DY42" t="n">
+        <v>64.08848763804292</v>
+      </c>
+      <c r="DZ42" t="n">
+        <v>51.714451082964</v>
+      </c>
+      <c r="EA42" t="n">
+        <v>55.98379916045716</v>
+      </c>
+      <c r="EB42" t="n">
+        <v>54.31360114452115</v>
+      </c>
+      <c r="EC42" t="n">
+        <v>51.00763550128465</v>
+      </c>
+      <c r="ED42" t="n">
+        <v>55.66771636321689</v>
+      </c>
+      <c r="EE42" t="n">
+        <v>53.26779217525259</v>
+      </c>
+      <c r="EF42" t="n">
+        <v>50.68581573960522</v>
+      </c>
+      <c r="EG42" t="n">
+        <v>54.41235009143887</v>
+      </c>
+      <c r="EH42" t="n">
         <v>52.71798651604851</v>
-      </c>
-      <c r="DP42" t="n">
-        <v>53.26779217525259</v>
-      </c>
-      <c r="DQ42" t="n">
-        <v>56.48465183952614</v>
-      </c>
-      <c r="DR42" t="n">
-        <v>56.60642794632711</v>
-      </c>
-      <c r="DS42" t="n">
-        <v>49.83279365780958</v>
-      </c>
-      <c r="DT42" t="n">
-        <v>53.88614428288363</v>
-      </c>
-      <c r="DU42" t="n">
-        <v>53.61237412091314</v>
-      </c>
-      <c r="DV42" t="n">
-        <v>51.37257100924343</v>
-      </c>
-      <c r="DW42" t="n">
-        <v>50.68581573960522</v>
-      </c>
-      <c r="DX42" t="n">
-        <v>50.8277124201076</v>
-      </c>
-      <c r="DY42" t="n">
-        <v>51.00763550128465</v>
-      </c>
-      <c r="DZ42" t="n">
-        <v>51.86218133406767</v>
-      </c>
-      <c r="EA42" t="n">
-        <v>53.15559539689821</v>
-      </c>
-      <c r="EB42" t="n">
-        <v>64.08848763804292</v>
-      </c>
-      <c r="EC42" t="n">
-        <v>65.36693034912744</v>
-      </c>
-      <c r="ED42" t="n">
-        <v>55.17325698678211</v>
-      </c>
-      <c r="EE42" t="n">
-        <v>58.05879351413334</v>
-      </c>
-      <c r="EF42" t="n">
-        <v>54.31360114452115</v>
-      </c>
-      <c r="EG42" t="n">
-        <v>56.38251177574104</v>
-      </c>
-      <c r="EH42" t="n">
-        <v>55.66771636321689</v>
       </c>
     </row>
     <row r="43">
@@ -16959,85 +16975,85 @@
         <v>0</v>
       </c>
       <c r="DH43" t="n">
-        <v>49.56139348411854</v>
+        <v>51.6202299330042</v>
       </c>
       <c r="DI43" t="n">
-        <v>47.66787459282371</v>
+        <v>62.43932737179578</v>
       </c>
       <c r="DJ43" t="n">
-        <v>51.6202299330042</v>
+        <v>49.90904691926842</v>
       </c>
       <c r="DK43" t="n">
-        <v>49.90904691926842</v>
+        <v>48.61316252075013</v>
       </c>
       <c r="DL43" t="n">
-        <v>52.2265966576512</v>
+        <v>51.27077962943323</v>
       </c>
       <c r="DM43" t="n">
-        <v>53.57767019255567</v>
+        <v>49.15724921043389</v>
       </c>
       <c r="DN43" t="n">
         <v>49.65145534197276</v>
       </c>
       <c r="DO43" t="n">
+        <v>51.5818945679484</v>
+      </c>
+      <c r="DP43" t="n">
+        <v>54.05445708873724</v>
+      </c>
+      <c r="DQ43" t="n">
+        <v>54.63212860026991</v>
+      </c>
+      <c r="DR43" t="n">
+        <v>47.66353393526713</v>
+      </c>
+      <c r="DS43" t="n">
+        <v>53.69845487673204</v>
+      </c>
+      <c r="DT43" t="n">
+        <v>49.48738910217254</v>
+      </c>
+      <c r="DU43" t="n">
+        <v>50.73421911081743</v>
+      </c>
+      <c r="DV43" t="n">
+        <v>47.66787459282371</v>
+      </c>
+      <c r="DW43" t="n">
+        <v>54.13677944591575</v>
+      </c>
+      <c r="DX43" t="n">
+        <v>52.61838048326824</v>
+      </c>
+      <c r="DY43" t="n">
+        <v>61.30059105032274</v>
+      </c>
+      <c r="DZ43" t="n">
+        <v>49.56139348411854</v>
+      </c>
+      <c r="EA43" t="n">
+        <v>53.57767019255567</v>
+      </c>
+      <c r="EB43" t="n">
+        <v>51.60000225420085</v>
+      </c>
+      <c r="EC43" t="n">
+        <v>48.75326259153329</v>
+      </c>
+      <c r="ED43" t="n">
+        <v>52.69188652563567</v>
+      </c>
+      <c r="EE43" t="n">
+        <v>51.01641591763868</v>
+      </c>
+      <c r="EF43" t="n">
+        <v>48.46403297146806</v>
+      </c>
+      <c r="EG43" t="n">
+        <v>52.2265966576512</v>
+      </c>
+      <c r="EH43" t="n">
         <v>50.49333231393762</v>
-      </c>
-      <c r="DP43" t="n">
-        <v>51.01641591763868</v>
-      </c>
-      <c r="DQ43" t="n">
-        <v>54.05445708873724</v>
-      </c>
-      <c r="DR43" t="n">
-        <v>54.13677944591575</v>
-      </c>
-      <c r="DS43" t="n">
-        <v>47.66353393526713</v>
-      </c>
-      <c r="DT43" t="n">
-        <v>51.5818945679484</v>
-      </c>
-      <c r="DU43" t="n">
-        <v>51.27077962943323</v>
-      </c>
-      <c r="DV43" t="n">
-        <v>49.15724921043389</v>
-      </c>
-      <c r="DW43" t="n">
-        <v>48.46403297146806</v>
-      </c>
-      <c r="DX43" t="n">
-        <v>48.61316252075013</v>
-      </c>
-      <c r="DY43" t="n">
-        <v>48.75326259153329</v>
-      </c>
-      <c r="DZ43" t="n">
-        <v>49.48738910217254</v>
-      </c>
-      <c r="EA43" t="n">
-        <v>50.73421911081743</v>
-      </c>
-      <c r="EB43" t="n">
-        <v>61.30059105032274</v>
-      </c>
-      <c r="EC43" t="n">
-        <v>62.43932737179578</v>
-      </c>
-      <c r="ED43" t="n">
-        <v>52.61838048326824</v>
-      </c>
-      <c r="EE43" t="n">
-        <v>54.63212860026991</v>
-      </c>
-      <c r="EF43" t="n">
-        <v>51.60000225420085</v>
-      </c>
-      <c r="EG43" t="n">
-        <v>53.69845487673204</v>
-      </c>
-      <c r="EH43" t="n">
-        <v>52.69188652563567</v>
       </c>
     </row>
     <row r="44">
@@ -17381,85 +17397,85 @@
         <v>0</v>
       </c>
       <c r="DH44" t="n">
-        <v>53.71628446902239</v>
+        <v>55.30887202947071</v>
       </c>
       <c r="DI44" t="n">
-        <v>52.36053772241289</v>
+        <v>64.85735503558828</v>
       </c>
       <c r="DJ44" t="n">
-        <v>55.30887202947071</v>
+        <v>54.08125814750094</v>
       </c>
       <c r="DK44" t="n">
-        <v>54.08125814750094</v>
+        <v>50.57275904942627</v>
       </c>
       <c r="DL44" t="n">
-        <v>56.61302606503748</v>
+        <v>54.61581936910425</v>
       </c>
       <c r="DM44" t="n">
-        <v>57.8285957048296</v>
+        <v>52.27984924419948</v>
       </c>
       <c r="DN44" t="n">
         <v>52.3945428204707</v>
       </c>
       <c r="DO44" t="n">
+        <v>54.87777045118359</v>
+      </c>
+      <c r="DP44" t="n">
+        <v>57.62228719865943</v>
+      </c>
+      <c r="DQ44" t="n">
+        <v>56.29487478429253</v>
+      </c>
+      <c r="DR44" t="n">
+        <v>51.58192498039442</v>
+      </c>
+      <c r="DS44" t="n">
+        <v>55.79610998850471</v>
+      </c>
+      <c r="DT44" t="n">
+        <v>51.57107568307799</v>
+      </c>
+      <c r="DU44" t="n">
+        <v>52.36280677043924</v>
+      </c>
+      <c r="DV44" t="n">
+        <v>52.36053772241289</v>
+      </c>
+      <c r="DW44" t="n">
+        <v>57.53052160813291</v>
+      </c>
+      <c r="DX44" t="n">
+        <v>54.05955077322833</v>
+      </c>
+      <c r="DY44" t="n">
+        <v>63.16769847610485</v>
+      </c>
+      <c r="DZ44" t="n">
+        <v>53.71628446902239</v>
+      </c>
+      <c r="EA44" t="n">
+        <v>57.8285957048296</v>
+      </c>
+      <c r="EB44" t="n">
+        <v>53.64337160943541</v>
+      </c>
+      <c r="EC44" t="n">
+        <v>50.80980806986758</v>
+      </c>
+      <c r="ED44" t="n">
+        <v>50.55814004379017</v>
+      </c>
+      <c r="EE44" t="n">
+        <v>53.50322772721827</v>
+      </c>
+      <c r="EF44" t="n">
+        <v>50.88174366225012</v>
+      </c>
+      <c r="EG44" t="n">
+        <v>56.61302606503748</v>
+      </c>
+      <c r="EH44" t="n">
         <v>53.34510532734048</v>
-      </c>
-      <c r="DP44" t="n">
-        <v>53.50322772721827</v>
-      </c>
-      <c r="DQ44" t="n">
-        <v>57.62228719865943</v>
-      </c>
-      <c r="DR44" t="n">
-        <v>57.53052160813291</v>
-      </c>
-      <c r="DS44" t="n">
-        <v>51.58192498039442</v>
-      </c>
-      <c r="DT44" t="n">
-        <v>54.87777045118359</v>
-      </c>
-      <c r="DU44" t="n">
-        <v>54.61581936910425</v>
-      </c>
-      <c r="DV44" t="n">
-        <v>52.27984924419948</v>
-      </c>
-      <c r="DW44" t="n">
-        <v>50.88174366225012</v>
-      </c>
-      <c r="DX44" t="n">
-        <v>50.57275904942627</v>
-      </c>
-      <c r="DY44" t="n">
-        <v>50.80980806986758</v>
-      </c>
-      <c r="DZ44" t="n">
-        <v>51.57107568307799</v>
-      </c>
-      <c r="EA44" t="n">
-        <v>52.36280677043924</v>
-      </c>
-      <c r="EB44" t="n">
-        <v>63.16769847610485</v>
-      </c>
-      <c r="EC44" t="n">
-        <v>64.85735503558828</v>
-      </c>
-      <c r="ED44" t="n">
-        <v>54.05955077322833</v>
-      </c>
-      <c r="EE44" t="n">
-        <v>56.29487478429253</v>
-      </c>
-      <c r="EF44" t="n">
-        <v>53.64337160943541</v>
-      </c>
-      <c r="EG44" t="n">
-        <v>55.79610998850471</v>
-      </c>
-      <c r="EH44" t="n">
-        <v>50.55814004379017</v>
       </c>
     </row>
     <row r="45">
@@ -17473,7 +17489,11 @@
           <t>ENDE GUARACACHI S.A.</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr"/>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
@@ -17612,13 +17632,13 @@
       <c r="EA45" t="inlineStr"/>
       <c r="EB45" t="inlineStr"/>
       <c r="EC45" t="inlineStr"/>
-      <c r="ED45" t="inlineStr"/>
+      <c r="ED45" t="n">
+        <v>61.8719098452103</v>
+      </c>
       <c r="EE45" t="inlineStr"/>
       <c r="EF45" t="inlineStr"/>
       <c r="EG45" t="inlineStr"/>
-      <c r="EH45" t="n">
-        <v>61.8719098452103</v>
-      </c>
+      <c r="EH45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -17961,75 +17981,75 @@
         <v>81432.4325</v>
       </c>
       <c r="DH46" t="n">
-        <v>20.63394610284283</v>
+        <v>20.83518202855175</v>
       </c>
       <c r="DI46" t="n">
-        <v>21.15578034496693</v>
+        <v>22.01735871883371</v>
       </c>
       <c r="DJ46" t="n">
-        <v>20.83518202855175</v>
-      </c>
-      <c r="DK46" t="n">
         <v>21.17358318673034</v>
       </c>
+      <c r="DK46" t="inlineStr"/>
       <c r="DL46" t="n">
-        <v>24.98350290406187</v>
+        <v>25.31083000491254</v>
       </c>
       <c r="DM46" t="n">
-        <v>22.11667204544706</v>
+        <v>23.64866426133485</v>
       </c>
       <c r="DN46" t="inlineStr"/>
       <c r="DO46" t="n">
+        <v>23.17136339673455</v>
+      </c>
+      <c r="DP46" t="n">
+        <v>31.38515344207907</v>
+      </c>
+      <c r="DQ46" t="n">
+        <v>54.28015500163052</v>
+      </c>
+      <c r="DR46" t="inlineStr"/>
+      <c r="DS46" t="n">
+        <v>94.51302217667784</v>
+      </c>
+      <c r="DT46" t="n">
+        <v>40.9712096753196</v>
+      </c>
+      <c r="DU46" t="n">
+        <v>25.63263543520351</v>
+      </c>
+      <c r="DV46" t="n">
+        <v>21.15578034496693</v>
+      </c>
+      <c r="DW46" t="n">
+        <v>22.96183614484618</v>
+      </c>
+      <c r="DX46" t="n">
+        <v>87.21788408971767</v>
+      </c>
+      <c r="DY46" t="n">
+        <v>22.04452410561705</v>
+      </c>
+      <c r="DZ46" t="n">
+        <v>20.63394610284283</v>
+      </c>
+      <c r="EA46" t="n">
+        <v>22.11667204544706</v>
+      </c>
+      <c r="EB46" t="n">
+        <v>153.3645767498298</v>
+      </c>
+      <c r="EC46" t="inlineStr"/>
+      <c r="ED46" t="n">
+        <v>2332.979612346443</v>
+      </c>
+      <c r="EE46" t="inlineStr"/>
+      <c r="EF46" t="n">
+        <v>32.12043311726576</v>
+      </c>
+      <c r="EG46" t="n">
+        <v>24.98350290406187</v>
+      </c>
+      <c r="EH46" t="n">
         <v>23.06549257405478</v>
-      </c>
-      <c r="DP46" t="inlineStr"/>
-      <c r="DQ46" t="n">
-        <v>31.38515344207907</v>
-      </c>
-      <c r="DR46" t="n">
-        <v>22.96183614484618</v>
-      </c>
-      <c r="DS46" t="inlineStr"/>
-      <c r="DT46" t="n">
-        <v>23.17136339673455</v>
-      </c>
-      <c r="DU46" t="n">
-        <v>25.31083000491254</v>
-      </c>
-      <c r="DV46" t="n">
-        <v>23.64866426133485</v>
-      </c>
-      <c r="DW46" t="n">
-        <v>32.12043311726576</v>
-      </c>
-      <c r="DX46" t="inlineStr"/>
-      <c r="DY46" t="inlineStr"/>
-      <c r="DZ46" t="n">
-        <v>40.9712096753196</v>
-      </c>
-      <c r="EA46" t="n">
-        <v>25.63263543520351</v>
-      </c>
-      <c r="EB46" t="n">
-        <v>22.04452410561705</v>
-      </c>
-      <c r="EC46" t="n">
-        <v>22.01735871883371</v>
-      </c>
-      <c r="ED46" t="n">
-        <v>87.21788408971767</v>
-      </c>
-      <c r="EE46" t="n">
-        <v>54.28015500163052</v>
-      </c>
-      <c r="EF46" t="n">
-        <v>153.3645767498298</v>
-      </c>
-      <c r="EG46" t="n">
-        <v>94.51302217667784</v>
-      </c>
-      <c r="EH46" t="n">
-        <v>2332.979612346443</v>
       </c>
     </row>
     <row r="47">
@@ -18373,85 +18393,85 @@
         <v>3823607.343</v>
       </c>
       <c r="DH47" t="n">
-        <v>30.26407124801968</v>
+        <v>29.32212986234979</v>
       </c>
       <c r="DI47" t="n">
-        <v>32.96698618028883</v>
+        <v>34.71107618457686</v>
       </c>
       <c r="DJ47" t="n">
-        <v>29.32212986234979</v>
+        <v>29.44639980062968</v>
       </c>
       <c r="DK47" t="n">
-        <v>29.44639980062968</v>
+        <v>34.89039219676263</v>
       </c>
       <c r="DL47" t="n">
-        <v>30.66477212315862</v>
+        <v>30.93784812698535</v>
       </c>
       <c r="DM47" t="n">
-        <v>30.33241312455273</v>
+        <v>32.06241423275874</v>
       </c>
       <c r="DN47" t="n">
         <v>30.5442622621787</v>
       </c>
       <c r="DO47" t="n">
+        <v>30.99301348156386</v>
+      </c>
+      <c r="DP47" t="n">
+        <v>30.29334428449937</v>
+      </c>
+      <c r="DQ47" t="n">
+        <v>32.53167519794066</v>
+      </c>
+      <c r="DR47" t="n">
+        <v>32.23610581103531</v>
+      </c>
+      <c r="DS47" t="n">
+        <v>34.36188299351475</v>
+      </c>
+      <c r="DT47" t="n">
+        <v>33.51114238404825</v>
+      </c>
+      <c r="DU47" t="n">
+        <v>30.69523807085066</v>
+      </c>
+      <c r="DV47" t="n">
+        <v>32.96698618028883</v>
+      </c>
+      <c r="DW47" t="n">
+        <v>33.64568668147474</v>
+      </c>
+      <c r="DX47" t="n">
+        <v>33.8884510057589</v>
+      </c>
+      <c r="DY47" t="n">
+        <v>33.94750985239826</v>
+      </c>
+      <c r="DZ47" t="n">
+        <v>30.26407124801968</v>
+      </c>
+      <c r="EA47" t="n">
+        <v>30.33241312455273</v>
+      </c>
+      <c r="EB47" t="n">
+        <v>31.70440587719019</v>
+      </c>
+      <c r="EC47" t="n">
+        <v>35.10268469146914</v>
+      </c>
+      <c r="ED47" t="n">
+        <v>37.93508612828085</v>
+      </c>
+      <c r="EE47" t="n">
+        <v>30.19000867561819</v>
+      </c>
+      <c r="EF47" t="n">
+        <v>31.18621081966296</v>
+      </c>
+      <c r="EG47" t="n">
+        <v>30.66477212315862</v>
+      </c>
+      <c r="EH47" t="n">
         <v>29.88015171800824</v>
-      </c>
-      <c r="DP47" t="n">
-        <v>30.19000867561819</v>
-      </c>
-      <c r="DQ47" t="n">
-        <v>30.29334428449937</v>
-      </c>
-      <c r="DR47" t="n">
-        <v>33.64568668147474</v>
-      </c>
-      <c r="DS47" t="n">
-        <v>32.23610581103531</v>
-      </c>
-      <c r="DT47" t="n">
-        <v>30.99301348156386</v>
-      </c>
-      <c r="DU47" t="n">
-        <v>30.93784812698535</v>
-      </c>
-      <c r="DV47" t="n">
-        <v>32.06241423275874</v>
-      </c>
-      <c r="DW47" t="n">
-        <v>31.18621081966296</v>
-      </c>
-      <c r="DX47" t="n">
-        <v>34.89039219676263</v>
-      </c>
-      <c r="DY47" t="n">
-        <v>35.10268469146914</v>
-      </c>
-      <c r="DZ47" t="n">
-        <v>33.51114238404825</v>
-      </c>
-      <c r="EA47" t="n">
-        <v>30.69523807085066</v>
-      </c>
-      <c r="EB47" t="n">
-        <v>33.94750985239826</v>
-      </c>
-      <c r="EC47" t="n">
-        <v>34.71107618457686</v>
-      </c>
-      <c r="ED47" t="n">
-        <v>33.8884510057589</v>
-      </c>
-      <c r="EE47" t="n">
-        <v>32.53167519794066</v>
-      </c>
-      <c r="EF47" t="n">
-        <v>31.70440587719019</v>
-      </c>
-      <c r="EG47" t="n">
-        <v>34.36188299351475</v>
-      </c>
-      <c r="EH47" t="n">
-        <v>37.93508612828085</v>
       </c>
     </row>
     <row r="48">
@@ -18465,7 +18485,11 @@
           <t>ENDE GENERACION</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr"/>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="n">
@@ -18935,81 +18959,81 @@
         <v>0</v>
       </c>
       <c r="DH49" t="n">
-        <v>92.23720373278699</v>
+        <v>94.69927357966922</v>
       </c>
       <c r="DI49" t="n">
-        <v>89.99811398342636</v>
+        <v>117.5265915729122</v>
       </c>
       <c r="DJ49" t="n">
-        <v>94.69927357966922</v>
+        <v>92.35020268160125</v>
       </c>
       <c r="DK49" t="n">
-        <v>92.35020268160125</v>
-      </c>
-      <c r="DL49" t="n">
-        <v>97.82490697436245</v>
-      </c>
+        <v>89.52717743826491</v>
+      </c>
+      <c r="DL49" t="inlineStr"/>
       <c r="DM49" t="n">
-        <v>99.5552614916211</v>
+        <v>92.71283675235523</v>
       </c>
       <c r="DN49" t="n">
         <v>89.86384436213866</v>
       </c>
-      <c r="DO49" t="n">
+      <c r="DO49" t="inlineStr"/>
+      <c r="DP49" t="n">
+        <v>98.6461827907017</v>
+      </c>
+      <c r="DQ49" t="n">
+        <v>105.7004946103663</v>
+      </c>
+      <c r="DR49" t="n">
+        <v>90.13594287050975</v>
+      </c>
+      <c r="DS49" t="n">
+        <v>106.4717493595162</v>
+      </c>
+      <c r="DT49" t="n">
+        <v>91.5334739486788</v>
+      </c>
+      <c r="DU49" t="n">
+        <v>93.28244887862479</v>
+      </c>
+      <c r="DV49" t="n">
+        <v>89.99811398342636</v>
+      </c>
+      <c r="DW49" t="n">
+        <v>99.96754128669471</v>
+      </c>
+      <c r="DX49" t="n">
+        <v>101.1448593683752</v>
+      </c>
+      <c r="DY49" t="n">
+        <v>112.323831699061</v>
+      </c>
+      <c r="DZ49" t="n">
+        <v>92.23720373278699</v>
+      </c>
+      <c r="EA49" t="n">
+        <v>99.5552614916211</v>
+      </c>
+      <c r="EB49" t="n">
+        <v>102.5852849801002</v>
+      </c>
+      <c r="EC49" t="n">
+        <v>90.10732996059883</v>
+      </c>
+      <c r="ED49" t="n">
+        <v>106.4483052083228</v>
+      </c>
+      <c r="EE49" t="n">
+        <v>92.02612291283623</v>
+      </c>
+      <c r="EF49" t="n">
+        <v>89.03258373836999</v>
+      </c>
+      <c r="EG49" t="n">
+        <v>97.82490697436245</v>
+      </c>
+      <c r="EH49" t="n">
         <v>91.66450879721256</v>
-      </c>
-      <c r="DP49" t="n">
-        <v>92.02612291283623</v>
-      </c>
-      <c r="DQ49" t="n">
-        <v>98.6461827907017</v>
-      </c>
-      <c r="DR49" t="n">
-        <v>99.96754128669471</v>
-      </c>
-      <c r="DS49" t="n">
-        <v>90.13594287050975</v>
-      </c>
-      <c r="DT49" t="inlineStr"/>
-      <c r="DU49" t="inlineStr"/>
-      <c r="DV49" t="n">
-        <v>92.71283675235523</v>
-      </c>
-      <c r="DW49" t="n">
-        <v>89.03258373836999</v>
-      </c>
-      <c r="DX49" t="n">
-        <v>89.52717743826491</v>
-      </c>
-      <c r="DY49" t="n">
-        <v>90.10732996059883</v>
-      </c>
-      <c r="DZ49" t="n">
-        <v>91.5334739486788</v>
-      </c>
-      <c r="EA49" t="n">
-        <v>93.28244887862479</v>
-      </c>
-      <c r="EB49" t="n">
-        <v>112.323831699061</v>
-      </c>
-      <c r="EC49" t="n">
-        <v>117.5265915729122</v>
-      </c>
-      <c r="ED49" t="n">
-        <v>101.1448593683752</v>
-      </c>
-      <c r="EE49" t="n">
-        <v>105.7004946103663</v>
-      </c>
-      <c r="EF49" t="n">
-        <v>102.5852849801002</v>
-      </c>
-      <c r="EG49" t="n">
-        <v>106.4717493595162</v>
-      </c>
-      <c r="EH49" t="n">
-        <v>106.4483052083228</v>
       </c>
     </row>
     <row r="50">
@@ -19023,7 +19047,11 @@
           <t>ENDE GUARACACHI S.A.</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr"/>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr"/>
@@ -19152,20 +19180,20 @@
       <c r="DI50" t="inlineStr"/>
       <c r="DJ50" t="inlineStr"/>
       <c r="DK50" t="inlineStr"/>
-      <c r="DL50" t="inlineStr"/>
+      <c r="DL50" t="n">
+        <v>94.98210799206586</v>
+      </c>
       <c r="DM50" t="inlineStr"/>
       <c r="DN50" t="inlineStr"/>
-      <c r="DO50" t="inlineStr"/>
+      <c r="DO50" t="n">
+        <v>95.79773921154981</v>
+      </c>
       <c r="DP50" t="inlineStr"/>
       <c r="DQ50" t="inlineStr"/>
       <c r="DR50" t="inlineStr"/>
       <c r="DS50" t="inlineStr"/>
-      <c r="DT50" t="n">
-        <v>95.79773921154981</v>
-      </c>
-      <c r="DU50" t="n">
-        <v>94.98210799206586</v>
-      </c>
+      <c r="DT50" t="inlineStr"/>
+      <c r="DU50" t="inlineStr"/>
       <c r="DV50" t="inlineStr"/>
       <c r="DW50" t="inlineStr"/>
       <c r="DX50" t="inlineStr"/>
@@ -19521,85 +19549,85 @@
         <v>1315577.515784552</v>
       </c>
       <c r="DH51" t="n">
-        <v>33.66375430732452</v>
+        <v>32.31176174482109</v>
       </c>
       <c r="DI51" t="n">
-        <v>33.36064478484334</v>
+        <v>56.09461201206894</v>
       </c>
       <c r="DJ51" t="n">
-        <v>32.31176174482109</v>
+        <v>34.31686992904541</v>
       </c>
       <c r="DK51" t="n">
-        <v>34.31686992904541</v>
+        <v>37.5461599584136</v>
       </c>
       <c r="DL51" t="n">
-        <v>37.23870536261955</v>
+        <v>35.09302858328922</v>
       </c>
       <c r="DM51" t="n">
-        <v>46.53841416155701</v>
+        <v>31.92752619158619</v>
       </c>
       <c r="DN51" t="n">
         <v>48.30322588309092</v>
       </c>
       <c r="DO51" t="n">
+        <v>40.25067688952186</v>
+      </c>
+      <c r="DP51" t="n">
+        <v>46.51817735868297</v>
+      </c>
+      <c r="DQ51" t="n">
+        <v>33.17975226294801</v>
+      </c>
+      <c r="DR51" t="n">
+        <v>30.85554123125481</v>
+      </c>
+      <c r="DS51" t="n">
+        <v>33.38655211553841</v>
+      </c>
+      <c r="DT51" t="n">
+        <v>47.10396008895513</v>
+      </c>
+      <c r="DU51" t="n">
+        <v>48.14748016130879</v>
+      </c>
+      <c r="DV51" t="n">
+        <v>33.36064478484334</v>
+      </c>
+      <c r="DW51" t="n">
+        <v>40.69237929341951</v>
+      </c>
+      <c r="DX51" t="n">
+        <v>36.82203899920513</v>
+      </c>
+      <c r="DY51" t="n">
+        <v>59.75162663081338</v>
+      </c>
+      <c r="DZ51" t="n">
+        <v>33.66375430732452</v>
+      </c>
+      <c r="EA51" t="n">
+        <v>46.53841416155701</v>
+      </c>
+      <c r="EB51" t="n">
+        <v>32.40090367521773</v>
+      </c>
+      <c r="EC51" t="n">
+        <v>44.90264111936129</v>
+      </c>
+      <c r="ED51" t="n">
+        <v>47.74715248413219</v>
+      </c>
+      <c r="EE51" t="n">
+        <v>57.71871920217923</v>
+      </c>
+      <c r="EF51" t="n">
+        <v>33.570437985383</v>
+      </c>
+      <c r="EG51" t="n">
+        <v>37.23870536261955</v>
+      </c>
+      <c r="EH51" t="n">
         <v>54.21515125496233</v>
-      </c>
-      <c r="DP51" t="n">
-        <v>57.71871920217923</v>
-      </c>
-      <c r="DQ51" t="n">
-        <v>46.51817735868297</v>
-      </c>
-      <c r="DR51" t="n">
-        <v>40.69237929341951</v>
-      </c>
-      <c r="DS51" t="n">
-        <v>30.85554123125481</v>
-      </c>
-      <c r="DT51" t="n">
-        <v>40.25067688952186</v>
-      </c>
-      <c r="DU51" t="n">
-        <v>35.09302858328922</v>
-      </c>
-      <c r="DV51" t="n">
-        <v>31.92752619158619</v>
-      </c>
-      <c r="DW51" t="n">
-        <v>33.570437985383</v>
-      </c>
-      <c r="DX51" t="n">
-        <v>37.5461599584136</v>
-      </c>
-      <c r="DY51" t="n">
-        <v>44.90264111936129</v>
-      </c>
-      <c r="DZ51" t="n">
-        <v>47.10396008895513</v>
-      </c>
-      <c r="EA51" t="n">
-        <v>48.14748016130879</v>
-      </c>
-      <c r="EB51" t="n">
-        <v>59.75162663081338</v>
-      </c>
-      <c r="EC51" t="n">
-        <v>56.09461201206894</v>
-      </c>
-      <c r="ED51" t="n">
-        <v>36.82203899920513</v>
-      </c>
-      <c r="EE51" t="n">
-        <v>33.17975226294801</v>
-      </c>
-      <c r="EF51" t="n">
-        <v>32.40090367521773</v>
-      </c>
-      <c r="EG51" t="n">
-        <v>33.38655211553841</v>
-      </c>
-      <c r="EH51" t="n">
-        <v>47.74715248413219</v>
       </c>
     </row>
   </sheetData>
